--- a/public/planilha-validacao-local-mariah.xlsx
+++ b/public/planilha-validacao-local-mariah.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Triagem A↔B" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Painel-resumo" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -2404,7 +2404,7 @@
         <v/>
       </c>
       <c r="K4" s="7" t="str">
-        <f aca="false">IF(J4="","",IF(I4="Sim",  IF(J4&lt;=56,"I",IF(J4&lt;=123,"II",IF(J4&lt;=202,"III","IV"))),  IF(J4&lt;=50,"I",IF(J4&lt;=110,"II",IF(J4&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J4="","",IF(I4="Sim",  IF(J4&lt;=64,"I",IF(J4&lt;=141,"II",IF(J4&lt;=230,"III","IV"))),  IF(J4&lt;=58,"I",IF(J4&lt;=127,"II",IF(J4&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M4" s="6" t="s">
@@ -2435,7 +2435,7 @@
         <v/>
       </c>
       <c r="K5" s="7" t="str">
-        <f aca="false">IF(J5="","",IF(I5="Sim",  IF(J5&lt;=56,"I",IF(J5&lt;=123,"II",IF(J5&lt;=202,"III","IV"))),  IF(J5&lt;=50,"I",IF(J5&lt;=110,"II",IF(J5&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J5="","",IF(I5="Sim",  IF(J5&lt;=64,"I",IF(J5&lt;=141,"II",IF(J5&lt;=230,"III","IV"))),  IF(J5&lt;=58,"I",IF(J5&lt;=127,"II",IF(J5&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M5" s="7" t="s">
@@ -2468,7 +2468,7 @@
         <v/>
       </c>
       <c r="K6" s="7" t="str">
-        <f aca="false">IF(J6="","",IF(I6="Sim",  IF(J6&lt;=56,"I",IF(J6&lt;=123,"II",IF(J6&lt;=202,"III","IV"))),  IF(J6&lt;=50,"I",IF(J6&lt;=110,"II",IF(J6&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J6="","",IF(I6="Sim",  IF(J6&lt;=64,"I",IF(J6&lt;=141,"II",IF(J6&lt;=230,"III","IV"))),  IF(J6&lt;=58,"I",IF(J6&lt;=127,"II",IF(J6&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M6" s="7" t="s">
@@ -2501,7 +2501,7 @@
         <v/>
       </c>
       <c r="K7" s="7" t="str">
-        <f aca="false">IF(J7="","",IF(I7="Sim",  IF(J7&lt;=56,"I",IF(J7&lt;=123,"II",IF(J7&lt;=202,"III","IV"))),  IF(J7&lt;=50,"I",IF(J7&lt;=110,"II",IF(J7&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J7="","",IF(I7="Sim",  IF(J7&lt;=64,"I",IF(J7&lt;=141,"II",IF(J7&lt;=230,"III","IV"))),  IF(J7&lt;=58,"I",IF(J7&lt;=127,"II",IF(J7&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M7" s="7" t="s">
@@ -2534,7 +2534,7 @@
         <v/>
       </c>
       <c r="K8" s="7" t="str">
-        <f aca="false">IF(J8="","",IF(I8="Sim",  IF(J8&lt;=56,"I",IF(J8&lt;=123,"II",IF(J8&lt;=202,"III","IV"))),  IF(J8&lt;=50,"I",IF(J8&lt;=110,"II",IF(J8&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J8="","",IF(I8="Sim",  IF(J8&lt;=64,"I",IF(J8&lt;=141,"II",IF(J8&lt;=230,"III","IV"))),  IF(J8&lt;=58,"I",IF(J8&lt;=127,"II",IF(J8&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M8" s="7" t="s">
@@ -2567,7 +2567,7 @@
         <v/>
       </c>
       <c r="K9" s="7" t="str">
-        <f aca="false">IF(J9="","",IF(I9="Sim",  IF(J9&lt;=56,"I",IF(J9&lt;=123,"II",IF(J9&lt;=202,"III","IV"))),  IF(J9&lt;=50,"I",IF(J9&lt;=110,"II",IF(J9&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J9="","",IF(I9="Sim",  IF(J9&lt;=64,"I",IF(J9&lt;=141,"II",IF(J9&lt;=230,"III","IV"))),  IF(J9&lt;=58,"I",IF(J9&lt;=127,"II",IF(J9&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M9" s="17" t="s">
@@ -2597,7 +2597,7 @@
         <v/>
       </c>
       <c r="K10" s="7" t="str">
-        <f aca="false">IF(J10="","",IF(I10="Sim",  IF(J10&lt;=56,"I",IF(J10&lt;=123,"II",IF(J10&lt;=202,"III","IV"))),  IF(J10&lt;=50,"I",IF(J10&lt;=110,"II",IF(J10&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J10="","",IF(I10="Sim",  IF(J10&lt;=64,"I",IF(J10&lt;=141,"II",IF(J10&lt;=230,"III","IV"))),  IF(J10&lt;=58,"I",IF(J10&lt;=127,"II",IF(J10&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
         <v/>
       </c>
       <c r="K11" s="7" t="str">
-        <f aca="false">IF(J11="","",IF(I11="Sim",  IF(J11&lt;=56,"I",IF(J11&lt;=123,"II",IF(J11&lt;=202,"III","IV"))),  IF(J11&lt;=50,"I",IF(J11&lt;=110,"II",IF(J11&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J11="","",IF(I11="Sim",  IF(J11&lt;=64,"I",IF(J11&lt;=141,"II",IF(J11&lt;=230,"III","IV"))),  IF(J11&lt;=58,"I",IF(J11&lt;=127,"II",IF(J11&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M11" s="10" t="s">
@@ -2646,7 +2646,7 @@
         <v/>
       </c>
       <c r="K12" s="7" t="str">
-        <f aca="false">IF(J12="","",IF(I12="Sim",  IF(J12&lt;=56,"I",IF(J12&lt;=123,"II",IF(J12&lt;=202,"III","IV"))),  IF(J12&lt;=50,"I",IF(J12&lt;=110,"II",IF(J12&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J12="","",IF(I12="Sim",  IF(J12&lt;=64,"I",IF(J12&lt;=141,"II",IF(J12&lt;=230,"III","IV"))),  IF(J12&lt;=58,"I",IF(J12&lt;=127,"II",IF(J12&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M12" s="11" t="s">
@@ -2675,7 +2675,7 @@
         <v/>
       </c>
       <c r="K13" s="7" t="str">
-        <f aca="false">IF(J13="","",IF(I13="Sim",  IF(J13&lt;=56,"I",IF(J13&lt;=123,"II",IF(J13&lt;=202,"III","IV"))),  IF(J13&lt;=50,"I",IF(J13&lt;=110,"II",IF(J13&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J13="","",IF(I13="Sim",  IF(J13&lt;=64,"I",IF(J13&lt;=141,"II",IF(J13&lt;=230,"III","IV"))),  IF(J13&lt;=58,"I",IF(J13&lt;=127,"II",IF(J13&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M13" s="11" t="s">
@@ -2704,7 +2704,7 @@
         <v/>
       </c>
       <c r="K14" s="7" t="str">
-        <f aca="false">IF(J14="","",IF(I14="Sim",  IF(J14&lt;=56,"I",IF(J14&lt;=123,"II",IF(J14&lt;=202,"III","IV"))),  IF(J14&lt;=50,"I",IF(J14&lt;=110,"II",IF(J14&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J14="","",IF(I14="Sim",  IF(J14&lt;=64,"I",IF(J14&lt;=141,"II",IF(J14&lt;=230,"III","IV"))),  IF(J14&lt;=58,"I",IF(J14&lt;=127,"II",IF(J14&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M14" s="11" t="s">
@@ -2733,7 +2733,7 @@
         <v/>
       </c>
       <c r="K15" s="7" t="str">
-        <f aca="false">IF(J15="","",IF(I15="Sim",  IF(J15&lt;=56,"I",IF(J15&lt;=123,"II",IF(J15&lt;=202,"III","IV"))),  IF(J15&lt;=50,"I",IF(J15&lt;=110,"II",IF(J15&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J15="","",IF(I15="Sim",  IF(J15&lt;=64,"I",IF(J15&lt;=141,"II",IF(J15&lt;=230,"III","IV"))),  IF(J15&lt;=58,"I",IF(J15&lt;=127,"II",IF(J15&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M15" s="11" t="s">
@@ -2762,7 +2762,7 @@
         <v/>
       </c>
       <c r="K16" s="7" t="str">
-        <f aca="false">IF(J16="","",IF(I16="Sim",  IF(J16&lt;=56,"I",IF(J16&lt;=123,"II",IF(J16&lt;=202,"III","IV"))),  IF(J16&lt;=50,"I",IF(J16&lt;=110,"II",IF(J16&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J16="","",IF(I16="Sim",  IF(J16&lt;=64,"I",IF(J16&lt;=141,"II",IF(J16&lt;=230,"III","IV"))),  IF(J16&lt;=58,"I",IF(J16&lt;=127,"II",IF(J16&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
       <c r="M16" s="11" t="s">
@@ -2791,7 +2791,7 @@
         <v/>
       </c>
       <c r="K17" s="7" t="str">
-        <f aca="false">IF(J17="","",IF(I17="Sim",  IF(J17&lt;=56,"I",IF(J17&lt;=123,"II",IF(J17&lt;=202,"III","IV"))),  IF(J17&lt;=50,"I",IF(J17&lt;=110,"II",IF(J17&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J17="","",IF(I17="Sim",  IF(J17&lt;=64,"I",IF(J17&lt;=141,"II",IF(J17&lt;=230,"III","IV"))),  IF(J17&lt;=58,"I",IF(J17&lt;=127,"II",IF(J17&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="K18" s="7" t="str">
-        <f aca="false">IF(J18="","",IF(I18="Sim",  IF(J18&lt;=56,"I",IF(J18&lt;=123,"II",IF(J18&lt;=202,"III","IV"))),  IF(J18&lt;=50,"I",IF(J18&lt;=110,"II",IF(J18&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J18="","",IF(I18="Sim",  IF(J18&lt;=64,"I",IF(J18&lt;=141,"II",IF(J18&lt;=230,"III","IV"))),  IF(J18&lt;=58,"I",IF(J18&lt;=127,"II",IF(J18&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="K19" s="7" t="str">
-        <f aca="false">IF(J19="","",IF(I19="Sim",  IF(J19&lt;=56,"I",IF(J19&lt;=123,"II",IF(J19&lt;=202,"III","IV"))),  IF(J19&lt;=50,"I",IF(J19&lt;=110,"II",IF(J19&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J19="","",IF(I19="Sim",  IF(J19&lt;=64,"I",IF(J19&lt;=141,"II",IF(J19&lt;=230,"III","IV"))),  IF(J19&lt;=58,"I",IF(J19&lt;=127,"II",IF(J19&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
         <v/>
       </c>
       <c r="K20" s="7" t="str">
-        <f aca="false">IF(J20="","",IF(I20="Sim",  IF(J20&lt;=56,"I",IF(J20&lt;=123,"II",IF(J20&lt;=202,"III","IV"))),  IF(J20&lt;=50,"I",IF(J20&lt;=110,"II",IF(J20&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J20="","",IF(I20="Sim",  IF(J20&lt;=64,"I",IF(J20&lt;=141,"II",IF(J20&lt;=230,"III","IV"))),  IF(J20&lt;=58,"I",IF(J20&lt;=127,"II",IF(J20&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         <v/>
       </c>
       <c r="K21" s="7" t="str">
-        <f aca="false">IF(J21="","",IF(I21="Sim",  IF(J21&lt;=56,"I",IF(J21&lt;=123,"II",IF(J21&lt;=202,"III","IV"))),  IF(J21&lt;=50,"I",IF(J21&lt;=110,"II",IF(J21&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J21="","",IF(I21="Sim",  IF(J21&lt;=64,"I",IF(J21&lt;=141,"II",IF(J21&lt;=230,"III","IV"))),  IF(J21&lt;=58,"I",IF(J21&lt;=127,"II",IF(J21&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v/>
       </c>
       <c r="K22" s="7" t="str">
-        <f aca="false">IF(J22="","",IF(I22="Sim",  IF(J22&lt;=56,"I",IF(J22&lt;=123,"II",IF(J22&lt;=202,"III","IV"))),  IF(J22&lt;=50,"I",IF(J22&lt;=110,"II",IF(J22&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J22="","",IF(I22="Sim",  IF(J22&lt;=64,"I",IF(J22&lt;=141,"II",IF(J22&lt;=230,"III","IV"))),  IF(J22&lt;=58,"I",IF(J22&lt;=127,"II",IF(J22&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="K23" s="7" t="str">
-        <f aca="false">IF(J23="","",IF(I23="Sim",  IF(J23&lt;=56,"I",IF(J23&lt;=123,"II",IF(J23&lt;=202,"III","IV"))),  IF(J23&lt;=50,"I",IF(J23&lt;=110,"II",IF(J23&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J23="","",IF(I23="Sim",  IF(J23&lt;=64,"I",IF(J23&lt;=141,"II",IF(J23&lt;=230,"III","IV"))),  IF(J23&lt;=58,"I",IF(J23&lt;=127,"II",IF(J23&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
         <v/>
       </c>
       <c r="K24" s="7" t="str">
-        <f aca="false">IF(J24="","",IF(I24="Sim",  IF(J24&lt;=56,"I",IF(J24&lt;=123,"II",IF(J24&lt;=202,"III","IV"))),  IF(J24&lt;=50,"I",IF(J24&lt;=110,"II",IF(J24&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J24="","",IF(I24="Sim",  IF(J24&lt;=64,"I",IF(J24&lt;=141,"II",IF(J24&lt;=230,"III","IV"))),  IF(J24&lt;=58,"I",IF(J24&lt;=127,"II",IF(J24&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
         <v/>
       </c>
       <c r="K25" s="7" t="str">
-        <f aca="false">IF(J25="","",IF(I25="Sim",  IF(J25&lt;=56,"I",IF(J25&lt;=123,"II",IF(J25&lt;=202,"III","IV"))),  IF(J25&lt;=50,"I",IF(J25&lt;=110,"II",IF(J25&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J25="","",IF(I25="Sim",  IF(J25&lt;=64,"I",IF(J25&lt;=141,"II",IF(J25&lt;=230,"III","IV"))),  IF(J25&lt;=58,"I",IF(J25&lt;=127,"II",IF(J25&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
         <v/>
       </c>
       <c r="K26" s="7" t="str">
-        <f aca="false">IF(J26="","",IF(I26="Sim",  IF(J26&lt;=56,"I",IF(J26&lt;=123,"II",IF(J26&lt;=202,"III","IV"))),  IF(J26&lt;=50,"I",IF(J26&lt;=110,"II",IF(J26&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J26="","",IF(I26="Sim",  IF(J26&lt;=64,"I",IF(J26&lt;=141,"II",IF(J26&lt;=230,"III","IV"))),  IF(J26&lt;=58,"I",IF(J26&lt;=127,"II",IF(J26&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
         <v/>
       </c>
       <c r="K27" s="7" t="str">
-        <f aca="false">IF(J27="","",IF(I27="Sim",  IF(J27&lt;=56,"I",IF(J27&lt;=123,"II",IF(J27&lt;=202,"III","IV"))),  IF(J27&lt;=50,"I",IF(J27&lt;=110,"II",IF(J27&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J27="","",IF(I27="Sim",  IF(J27&lt;=64,"I",IF(J27&lt;=141,"II",IF(J27&lt;=230,"III","IV"))),  IF(J27&lt;=58,"I",IF(J27&lt;=127,"II",IF(J27&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
         <v/>
       </c>
       <c r="K28" s="7" t="str">
-        <f aca="false">IF(J28="","",IF(I28="Sim",  IF(J28&lt;=56,"I",IF(J28&lt;=123,"II",IF(J28&lt;=202,"III","IV"))),  IF(J28&lt;=50,"I",IF(J28&lt;=110,"II",IF(J28&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J28="","",IF(I28="Sim",  IF(J28&lt;=64,"I",IF(J28&lt;=141,"II",IF(J28&lt;=230,"III","IV"))),  IF(J28&lt;=58,"I",IF(J28&lt;=127,"II",IF(J28&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
         <v/>
       </c>
       <c r="K29" s="7" t="str">
-        <f aca="false">IF(J29="","",IF(I29="Sim",  IF(J29&lt;=56,"I",IF(J29&lt;=123,"II",IF(J29&lt;=202,"III","IV"))),  IF(J29&lt;=50,"I",IF(J29&lt;=110,"II",IF(J29&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J29="","",IF(I29="Sim",  IF(J29&lt;=64,"I",IF(J29&lt;=141,"II",IF(J29&lt;=230,"III","IV"))),  IF(J29&lt;=58,"I",IF(J29&lt;=127,"II",IF(J29&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="K30" s="7" t="str">
-        <f aca="false">IF(J30="","",IF(I30="Sim",  IF(J30&lt;=56,"I",IF(J30&lt;=123,"II",IF(J30&lt;=202,"III","IV"))),  IF(J30&lt;=50,"I",IF(J30&lt;=110,"II",IF(J30&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J30="","",IF(I30="Sim",  IF(J30&lt;=64,"I",IF(J30&lt;=141,"II",IF(J30&lt;=230,"III","IV"))),  IF(J30&lt;=58,"I",IF(J30&lt;=127,"II",IF(J30&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="K31" s="7" t="str">
-        <f aca="false">IF(J31="","",IF(I31="Sim",  IF(J31&lt;=56,"I",IF(J31&lt;=123,"II",IF(J31&lt;=202,"III","IV"))),  IF(J31&lt;=50,"I",IF(J31&lt;=110,"II",IF(J31&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J31="","",IF(I31="Sim",  IF(J31&lt;=64,"I",IF(J31&lt;=141,"II",IF(J31&lt;=230,"III","IV"))),  IF(J31&lt;=58,"I",IF(J31&lt;=127,"II",IF(J31&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v/>
       </c>
       <c r="K32" s="7" t="str">
-        <f aca="false">IF(J32="","",IF(I32="Sim",  IF(J32&lt;=56,"I",IF(J32&lt;=123,"II",IF(J32&lt;=202,"III","IV"))),  IF(J32&lt;=50,"I",IF(J32&lt;=110,"II",IF(J32&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J32="","",IF(I32="Sim",  IF(J32&lt;=64,"I",IF(J32&lt;=141,"II",IF(J32&lt;=230,"III","IV"))),  IF(J32&lt;=58,"I",IF(J32&lt;=127,"II",IF(J32&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         <v/>
       </c>
       <c r="K33" s="7" t="str">
-        <f aca="false">IF(J33="","",IF(I33="Sim",  IF(J33&lt;=56,"I",IF(J33&lt;=123,"II",IF(J33&lt;=202,"III","IV"))),  IF(J33&lt;=50,"I",IF(J33&lt;=110,"II",IF(J33&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J33="","",IF(I33="Sim",  IF(J33&lt;=64,"I",IF(J33&lt;=141,"II",IF(J33&lt;=230,"III","IV"))),  IF(J33&lt;=58,"I",IF(J33&lt;=127,"II",IF(J33&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v/>
       </c>
       <c r="K34" s="7" t="str">
-        <f aca="false">IF(J34="","",IF(I34="Sim",  IF(J34&lt;=56,"I",IF(J34&lt;=123,"II",IF(J34&lt;=202,"III","IV"))),  IF(J34&lt;=50,"I",IF(J34&lt;=110,"II",IF(J34&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J34="","",IF(I34="Sim",  IF(J34&lt;=64,"I",IF(J34&lt;=141,"II",IF(J34&lt;=230,"III","IV"))),  IF(J34&lt;=58,"I",IF(J34&lt;=127,"II",IF(J34&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="K35" s="7" t="str">
-        <f aca="false">IF(J35="","",IF(I35="Sim",  IF(J35&lt;=56,"I",IF(J35&lt;=123,"II",IF(J35&lt;=202,"III","IV"))),  IF(J35&lt;=50,"I",IF(J35&lt;=110,"II",IF(J35&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J35="","",IF(I35="Sim",  IF(J35&lt;=64,"I",IF(J35&lt;=141,"II",IF(J35&lt;=230,"III","IV"))),  IF(J35&lt;=58,"I",IF(J35&lt;=127,"II",IF(J35&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="K36" s="7" t="str">
-        <f aca="false">IF(J36="","",IF(I36="Sim",  IF(J36&lt;=56,"I",IF(J36&lt;=123,"II",IF(J36&lt;=202,"III","IV"))),  IF(J36&lt;=50,"I",IF(J36&lt;=110,"II",IF(J36&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J36="","",IF(I36="Sim",  IF(J36&lt;=64,"I",IF(J36&lt;=141,"II",IF(J36&lt;=230,"III","IV"))),  IF(J36&lt;=58,"I",IF(J36&lt;=127,"II",IF(J36&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="K37" s="7" t="str">
-        <f aca="false">IF(J37="","",IF(I37="Sim",  IF(J37&lt;=56,"I",IF(J37&lt;=123,"II",IF(J37&lt;=202,"III","IV"))),  IF(J37&lt;=50,"I",IF(J37&lt;=110,"II",IF(J37&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J37="","",IF(I37="Sim",  IF(J37&lt;=64,"I",IF(J37&lt;=141,"II",IF(J37&lt;=230,"III","IV"))),  IF(J37&lt;=58,"I",IF(J37&lt;=127,"II",IF(J37&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
         <v/>
       </c>
       <c r="K38" s="7" t="str">
-        <f aca="false">IF(J38="","",IF(I38="Sim",  IF(J38&lt;=56,"I",IF(J38&lt;=123,"II",IF(J38&lt;=202,"III","IV"))),  IF(J38&lt;=50,"I",IF(J38&lt;=110,"II",IF(J38&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J38="","",IF(I38="Sim",  IF(J38&lt;=64,"I",IF(J38&lt;=141,"II",IF(J38&lt;=230,"III","IV"))),  IF(J38&lt;=58,"I",IF(J38&lt;=127,"II",IF(J38&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
         <v/>
       </c>
       <c r="K39" s="7" t="str">
-        <f aca="false">IF(J39="","",IF(I39="Sim",  IF(J39&lt;=56,"I",IF(J39&lt;=123,"II",IF(J39&lt;=202,"III","IV"))),  IF(J39&lt;=50,"I",IF(J39&lt;=110,"II",IF(J39&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J39="","",IF(I39="Sim",  IF(J39&lt;=64,"I",IF(J39&lt;=141,"II",IF(J39&lt;=230,"III","IV"))),  IF(J39&lt;=58,"I",IF(J39&lt;=127,"II",IF(J39&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v/>
       </c>
       <c r="K40" s="7" t="str">
-        <f aca="false">IF(J40="","",IF(I40="Sim",  IF(J40&lt;=56,"I",IF(J40&lt;=123,"II",IF(J40&lt;=202,"III","IV"))),  IF(J40&lt;=50,"I",IF(J40&lt;=110,"II",IF(J40&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J40="","",IF(I40="Sim",  IF(J40&lt;=64,"I",IF(J40&lt;=141,"II",IF(J40&lt;=230,"III","IV"))),  IF(J40&lt;=58,"I",IF(J40&lt;=127,"II",IF(J40&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
         <v/>
       </c>
       <c r="K41" s="7" t="str">
-        <f aca="false">IF(J41="","",IF(I41="Sim",  IF(J41&lt;=56,"I",IF(J41&lt;=123,"II",IF(J41&lt;=202,"III","IV"))),  IF(J41&lt;=50,"I",IF(J41&lt;=110,"II",IF(J41&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J41="","",IF(I41="Sim",  IF(J41&lt;=64,"I",IF(J41&lt;=141,"II",IF(J41&lt;=230,"III","IV"))),  IF(J41&lt;=58,"I",IF(J41&lt;=127,"II",IF(J41&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
         <v/>
       </c>
       <c r="K42" s="7" t="str">
-        <f aca="false">IF(J42="","",IF(I42="Sim",  IF(J42&lt;=56,"I",IF(J42&lt;=123,"II",IF(J42&lt;=202,"III","IV"))),  IF(J42&lt;=50,"I",IF(J42&lt;=110,"II",IF(J42&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J42="","",IF(I42="Sim",  IF(J42&lt;=64,"I",IF(J42&lt;=141,"II",IF(J42&lt;=230,"III","IV"))),  IF(J42&lt;=58,"I",IF(J42&lt;=127,"II",IF(J42&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         <v/>
       </c>
       <c r="K43" s="7" t="str">
-        <f aca="false">IF(J43="","",IF(I43="Sim",  IF(J43&lt;=56,"I",IF(J43&lt;=123,"II",IF(J43&lt;=202,"III","IV"))),  IF(J43&lt;=50,"I",IF(J43&lt;=110,"II",IF(J43&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J43="","",IF(I43="Sim",  IF(J43&lt;=64,"I",IF(J43&lt;=141,"II",IF(J43&lt;=230,"III","IV"))),  IF(J43&lt;=58,"I",IF(J43&lt;=127,"II",IF(J43&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
         <v/>
       </c>
       <c r="K44" s="7" t="str">
-        <f aca="false">IF(J44="","",IF(I44="Sim",  IF(J44&lt;=56,"I",IF(J44&lt;=123,"II",IF(J44&lt;=202,"III","IV"))),  IF(J44&lt;=50,"I",IF(J44&lt;=110,"II",IF(J44&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J44="","",IF(I44="Sim",  IF(J44&lt;=64,"I",IF(J44&lt;=141,"II",IF(J44&lt;=230,"III","IV"))),  IF(J44&lt;=58,"I",IF(J44&lt;=127,"II",IF(J44&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         <v/>
       </c>
       <c r="K45" s="7" t="str">
-        <f aca="false">IF(J45="","",IF(I45="Sim",  IF(J45&lt;=56,"I",IF(J45&lt;=123,"II",IF(J45&lt;=202,"III","IV"))),  IF(J45&lt;=50,"I",IF(J45&lt;=110,"II",IF(J45&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J45="","",IF(I45="Sim",  IF(J45&lt;=64,"I",IF(J45&lt;=141,"II",IF(J45&lt;=230,"III","IV"))),  IF(J45&lt;=58,"I",IF(J45&lt;=127,"II",IF(J45&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
         <v/>
       </c>
       <c r="K46" s="7" t="str">
-        <f aca="false">IF(J46="","",IF(I46="Sim",  IF(J46&lt;=56,"I",IF(J46&lt;=123,"II",IF(J46&lt;=202,"III","IV"))),  IF(J46&lt;=50,"I",IF(J46&lt;=110,"II",IF(J46&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J46="","",IF(I46="Sim",  IF(J46&lt;=64,"I",IF(J46&lt;=141,"II",IF(J46&lt;=230,"III","IV"))),  IF(J46&lt;=58,"I",IF(J46&lt;=127,"II",IF(J46&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         <v/>
       </c>
       <c r="K47" s="7" t="str">
-        <f aca="false">IF(J47="","",IF(I47="Sim",  IF(J47&lt;=56,"I",IF(J47&lt;=123,"II",IF(J47&lt;=202,"III","IV"))),  IF(J47&lt;=50,"I",IF(J47&lt;=110,"II",IF(J47&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J47="","",IF(I47="Sim",  IF(J47&lt;=64,"I",IF(J47&lt;=141,"II",IF(J47&lt;=230,"III","IV"))),  IF(J47&lt;=58,"I",IF(J47&lt;=127,"II",IF(J47&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="K48" s="7" t="str">
-        <f aca="false">IF(J48="","",IF(I48="Sim",  IF(J48&lt;=56,"I",IF(J48&lt;=123,"II",IF(J48&lt;=202,"III","IV"))),  IF(J48&lt;=50,"I",IF(J48&lt;=110,"II",IF(J48&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J48="","",IF(I48="Sim",  IF(J48&lt;=64,"I",IF(J48&lt;=141,"II",IF(J48&lt;=230,"III","IV"))),  IF(J48&lt;=58,"I",IF(J48&lt;=127,"II",IF(J48&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
         <v/>
       </c>
       <c r="K49" s="7" t="str">
-        <f aca="false">IF(J49="","",IF(I49="Sim",  IF(J49&lt;=56,"I",IF(J49&lt;=123,"II",IF(J49&lt;=202,"III","IV"))),  IF(J49&lt;=50,"I",IF(J49&lt;=110,"II",IF(J49&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J49="","",IF(I49="Sim",  IF(J49&lt;=64,"I",IF(J49&lt;=141,"II",IF(J49&lt;=230,"III","IV"))),  IF(J49&lt;=58,"I",IF(J49&lt;=127,"II",IF(J49&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
         <v/>
       </c>
       <c r="K50" s="7" t="str">
-        <f aca="false">IF(J50="","",IF(I50="Sim",  IF(J50&lt;=56,"I",IF(J50&lt;=123,"II",IF(J50&lt;=202,"III","IV"))),  IF(J50&lt;=50,"I",IF(J50&lt;=110,"II",IF(J50&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J50="","",IF(I50="Sim",  IF(J50&lt;=64,"I",IF(J50&lt;=141,"II",IF(J50&lt;=230,"III","IV"))),  IF(J50&lt;=58,"I",IF(J50&lt;=127,"II",IF(J50&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
         <v/>
       </c>
       <c r="K51" s="7" t="str">
-        <f aca="false">IF(J51="","",IF(I51="Sim",  IF(J51&lt;=56,"I",IF(J51&lt;=123,"II",IF(J51&lt;=202,"III","IV"))),  IF(J51&lt;=50,"I",IF(J51&lt;=110,"II",IF(J51&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J51="","",IF(I51="Sim",  IF(J51&lt;=64,"I",IF(J51&lt;=141,"II",IF(J51&lt;=230,"III","IV"))),  IF(J51&lt;=58,"I",IF(J51&lt;=127,"II",IF(J51&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
         <v/>
       </c>
       <c r="K52" s="7" t="str">
-        <f aca="false">IF(J52="","",IF(I52="Sim",  IF(J52&lt;=56,"I",IF(J52&lt;=123,"II",IF(J52&lt;=202,"III","IV"))),  IF(J52&lt;=50,"I",IF(J52&lt;=110,"II",IF(J52&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J52="","",IF(I52="Sim",  IF(J52&lt;=64,"I",IF(J52&lt;=141,"II",IF(J52&lt;=230,"III","IV"))),  IF(J52&lt;=58,"I",IF(J52&lt;=127,"II",IF(J52&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
         <v/>
       </c>
       <c r="K53" s="7" t="str">
-        <f aca="false">IF(J53="","",IF(I53="Sim",  IF(J53&lt;=56,"I",IF(J53&lt;=123,"II",IF(J53&lt;=202,"III","IV"))),  IF(J53&lt;=50,"I",IF(J53&lt;=110,"II",IF(J53&lt;=180,"III","IV")))))</f>
+        <f aca="false">IF(J53="","",IF(I53="Sim",  IF(J53&lt;=64,"I",IF(J53&lt;=141,"II",IF(J53&lt;=230,"III","IV"))),  IF(J53&lt;=58,"I",IF(J53&lt;=127,"II",IF(J53&lt;=208,"III","IV")))))</f>
         <v/>
       </c>
     </row>

--- a/public/planilha-validacao-local-mariah.xlsx
+++ b/public/planilha-validacao-local-mariah.xlsx
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
   <si>
     <t xml:space="preserve">Planilha-modelo · Validação Local da MARIAH pelos CEPs</t>
   </si>
   <si>
-    <t xml:space="preserve">Esta planilha automatiza o registro e o cálculo dos indicadores das três frentes de validação propostas na Seção de Validação Local (Caderno 2). Use-a no Microsoft Excel, no LibreOffice Calc ou no Google Sheets — não requer instalação de extensão estatística.</t>
+    <t xml:space="preserve">Esta planilha automatiza o registro e o cálculo dos indicadores das três frentes de validação propostas na Seção de Validação Local do documento MARIAH. Use-a no Microsoft Excel, no LibreOffice Calc ou no Google Sheets — não requer instalação de extensão estatística.</t>
   </si>
   <si>
     <t xml:space="preserve">Como usar:</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">1. Aba «Protocolos» — cadastre cada protocolo com um identificador interno do CEP. Não registre dados que permitam identificar pesquisador, instituição proponente ou patrocinador. A planilha não pede esses dados.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Aba «Versão A» — para cada protocolo aplicado em paralelo por dois avaliadores, registre a classificação consolidada de cada avaliador (I, II, III ou IV). A planilha calcula automaticamente o percentual de concordância e a estatística kappa de Cohen, com leitura sugerida.</t>
+    <t xml:space="preserve">2. Aba «Versão A» — para cada protocolo aplicado em paralelo por dois avaliadores, registre a classificação consolidada de cada avaliador (I, II, III, IV ou NÃO AVALIÁVEL). A planilha calcula o percentual de concordância e a estatística kappa de Cohen sobre os pares com nível atribuído, com leitura sugerida, e a concordância quanto à avaliabilidade, que inclui os não avaliáveis.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Aba «Versão B» — para cada protocolo avaliado pela Versão B, registre a pontuação líquida por bloco (incluindo o Bloco 6.b, quando houver banco de dados) e marque, nas colunas próprias, se a Cláusula de Prevalência Ética foi acionada e se o protocolo foi declarado não avaliável. A planilha calcula a pontuação total e o nível resultante com as mesmas regras da MARIAH, e gera a distribuição da casuística do CEP nos quatro níveis.</t>
@@ -109,10 +109,10 @@
     <t xml:space="preserve">· Os cálculos são fórmulas Excel/Calc. Não delete células sombreadas (verde-claro). Edite apenas as células destacadas em amarelo-claro.</t>
   </si>
   <si>
-    <t xml:space="preserve">· O retorno opcional ao Grupo de Trabalho é descrito na Seção de Validação Local (Caderno 2). CEPs que optarem por compartilhar podem enviar a planilha completa ou apenas o painel-resumo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novidades da versão 2 desta planilha (25/09/2026):</t>
+    <t xml:space="preserve">· O retorno opcional ao Grupo de Trabalho é descrito na Seção de Validação Local do documento MARIAH. CEPs que optarem por compartilhar podem enviar a planilha completa ou apenas o painel-resumo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novidades da versão 2 desta planilha (25/09/2026; revisão 2.1):</t>
   </si>
   <si>
     <t xml:space="preserve">· Aba «Versão B»: coluna própria para o Bloco 6.b (antes somado à mão ao Bloco 6); colunas «Cláusula de Prevalência?» e «Não avaliável?»; o «Nível» passa a IV quando a Cláusula é acionada e a «NÃO AVALIÁVEL» quando há eliminatória — antes era calculado só pela pontuação e podia divergir da MARIAH. Não avaliáveis saem da distribuição e das estatísticas. Listas de seleção nas colunas Sim/Não.</t>
@@ -121,6 +121,9 @@
     <t xml:space="preserve">· Aba «Triagem A↔B» e «Painel-resumo»: passam a ler o nível corrigido; pares com protocolo não avaliável ficam fora da convergência.</t>
   </si>
   <si>
+    <t xml:space="preserve">· Aba «Versão A» (revisão 2.1): aceita NÃO AVALIÁVEL; o kappa usa só os pares com nível I–IV e um indicador próprio mede a concordância quanto à avaliabilidade. Nomenclatura: a Seção de Validação Local é citada como parte do documento MARIAH.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cadastro de protocolos avaliados</t>
   </si>
   <si>
@@ -145,7 +148,7 @@
     <t xml:space="preserve">Versão A — Concordância entre avaliadores</t>
   </si>
   <si>
-    <t xml:space="preserve">Para cada protocolo, registre a classificação consolidada do Avaliador 1 e do Avaliador 2 (I, II, III ou IV). A planilha calcula automaticamente, no painel à direita, o percentual de concordância e o kappa de Cohen.</t>
+    <t xml:space="preserve">Para cada protocolo, registre a classificação consolidada do Avaliador 1 e do Avaliador 2: I, II, III, IV ou NÃO AVALIÁVEL (quando a MARIAH declarou o protocolo não avaliável). O kappa de Cohen é calculado só com os pares em que os dois avaliadores atribuíram nível (I a IV); a concordância quanto à avaliabilidade, que inclui os NÃO AVALIÁVEIS, aparece à parte, no painel à direita.</t>
   </si>
   <si>
     <t xml:space="preserve">Avaliador 1 (I/II/III/IV)</t>
@@ -163,7 +166,7 @@
     <t xml:space="preserve">Indicadores</t>
   </si>
   <si>
-    <t xml:space="preserve">n de protocolos avaliados em par</t>
+    <t xml:space="preserve">n de pares com nível I–IV (base do kappa)</t>
   </si>
   <si>
     <t xml:space="preserve">concordâncias (n)</t>
@@ -187,6 +190,18 @@
     <t xml:space="preserve">Faixas de leitura segundo Landis &amp; Koch (1977).</t>
   </si>
   <si>
+    <t xml:space="preserve">Avaliabilidade (inclui NÃO AVALIÁVEL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pares com as duas classificações registradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pares com NÃO AVALIÁVEL (fora do kappa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concordância quanto à avaliabilidade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Versão B — Pontuação por bloco e distribuição</t>
   </si>
   <si>
@@ -350,6 +365,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;0,40 Insuficiente · 0,40–0,60 Moderada · 0,60–0,80 Substancial · ≥0,80 Quase perfeita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concordância quanto à avaliabilidade (inclui NÃO AVALIÁVEL)</t>
   </si>
   <si>
     <t xml:space="preserve">Frente 2 — Distribuição empírica da casuística (Versão B)</t>
@@ -486,8 +504,8 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF555555"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -499,8 +517,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF555555"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -607,7 +625,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -628,7 +646,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -688,11 +706,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -708,11 +738,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -724,11 +754,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,6 +784,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1020,7 +1050,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
@@ -1127,19 +1157,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1168,7 +1203,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1177,7 +1212,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1186,19 +1221,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1577,13 +1612,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1592,7 +1627,7 @@
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1601,22 +1636,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="12"/>
     </row>
@@ -1628,18 +1663,18 @@
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="13" t="str">
-        <f aca="false">IF(OR(B4="",C4=""),"",IF(B4=C4,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B4="",C4=""),"",IF(AND(ISNUMBER(MATCH(B4,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C4,{"I","II","III","IV"},0))),IF(B4=C4,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E4" s="13" t="str">
-        <f aca="false">IF(OR(B4="",C4=""),"",ABS(MATCH(B4,{"I","II","III","IV"},0)-MATCH(C4,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B4="",C4=""),"",IF(AND(ISNUMBER(MATCH(B4,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C4,{"I","II","III","IV"},0))),ABS(MATCH(B4,{"I","II","III","IV"},0)-MATCH(C4,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G4" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="16" t="n">
-        <f aca="false">COUNTIFS(B4:B53,"&lt;&gt;",C4:C53,"&lt;&gt;")</f>
+        <f aca="false">SUMPRODUCT(ISNUMBER(MATCH(B4:B53,{"I","II","III","IV"},0))*ISNUMBER(MATCH(C4:C53,{"I","II","III","IV"},0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -1651,15 +1686,15 @@
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="13" t="str">
-        <f aca="false">IF(OR(B5="",C5=""),"",IF(B5=C5,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B5="",C5=""),"",IF(AND(ISNUMBER(MATCH(B5,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C5,{"I","II","III","IV"},0))),IF(B5=C5,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E5" s="13" t="str">
-        <f aca="false">IF(OR(B5="",C5=""),"",ABS(MATCH(B5,{"I","II","III","IV"},0)-MATCH(C5,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B5="",C5=""),"",IF(AND(ISNUMBER(MATCH(B5,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C5,{"I","II","III","IV"},0))),ABS(MATCH(B5,{"I","II","III","IV"},0)-MATCH(C5,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G5" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="false">COUNTIF(D4:D53,"Sim")</f>
@@ -1674,15 +1709,15 @@
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="13" t="str">
-        <f aca="false">IF(OR(B6="",C6=""),"",IF(B6=C6,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B6="",C6=""),"",IF(AND(ISNUMBER(MATCH(B6,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C6,{"I","II","III","IV"},0))),IF(B6=C6,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E6" s="13" t="str">
-        <f aca="false">IF(OR(B6="",C6=""),"",ABS(MATCH(B6,{"I","II","III","IV"},0)-MATCH(C6,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B6="",C6=""),"",IF(AND(ISNUMBER(MATCH(B6,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C6,{"I","II","III","IV"},0))),ABS(MATCH(B6,{"I","II","III","IV"},0)-MATCH(C6,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G6" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" s="16" t="n">
         <f aca="false">COUNTIF(D4:D53,"Não")</f>
@@ -1697,15 +1732,15 @@
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="13" t="str">
-        <f aca="false">IF(OR(B7="",C7=""),"",IF(B7=C7,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B7="",C7=""),"",IF(AND(ISNUMBER(MATCH(B7,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C7,{"I","II","III","IV"},0))),IF(B7=C7,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E7" s="13" t="str">
-        <f aca="false">IF(OR(B7="",C7=""),"",ABS(MATCH(B7,{"I","II","III","IV"},0)-MATCH(C7,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B7="",C7=""),"",IF(AND(ISNUMBER(MATCH(B7,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C7,{"I","II","III","IV"},0))),ABS(MATCH(B7,{"I","II","III","IV"},0)-MATCH(C7,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G7" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="17" t="str">
         <f aca="false">IF(H4=0,"",H5/H4)</f>
@@ -1720,18 +1755,18 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="13" t="str">
-        <f aca="false">IF(OR(B8="",C8=""),"",IF(B8=C8,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B8="",C8=""),"",IF(AND(ISNUMBER(MATCH(B8,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C8,{"I","II","III","IV"},0))),IF(B8=C8,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E8" s="13" t="str">
-        <f aca="false">IF(OR(B8="",C8=""),"",ABS(MATCH(B8,{"I","II","III","IV"},0)-MATCH(C8,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B8="",C8=""),"",IF(AND(ISNUMBER(MATCH(B8,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C8,{"I","II","III","IV"},0))),ABS(MATCH(B8,{"I","II","III","IV"},0)-MATCH(C8,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G8" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" s="17" t="str">
-        <f aca="false">IF(H4=0,"",(COUNTIF(B4:B53,"I")*COUNTIF(C4:C53,"I")+COUNTIF(B4:B53,"II")*COUNTIF(C4:C53,"II")+COUNTIF(B4:B53,"III")*COUNTIF(C4:C53,"III")+COUNTIF(B4:B53,"IV")*COUNTIF(C4:C53,"IV"))/(H4*H4))</f>
+        <f aca="false">IF(H4=0,"",(SUMPRODUCT((B4:B53="I")*ISNUMBER(MATCH(C4:C53,{"I","II","III","IV"},0)))*SUMPRODUCT((C4:C53="I")*ISNUMBER(MATCH(B4:B53,{"I","II","III","IV"},0)))+SUMPRODUCT((B4:B53="II")*ISNUMBER(MATCH(C4:C53,{"I","II","III","IV"},0)))*SUMPRODUCT((C4:C53="II")*ISNUMBER(MATCH(B4:B53,{"I","II","III","IV"},0)))+SUMPRODUCT((B4:B53="III")*ISNUMBER(MATCH(C4:C53,{"I","II","III","IV"},0)))*SUMPRODUCT((C4:C53="III")*ISNUMBER(MATCH(B4:B53,{"I","II","III","IV"},0)))+SUMPRODUCT((B4:B53="IV")*ISNUMBER(MATCH(C4:C53,{"I","II","III","IV"},0)))*SUMPRODUCT((C4:C53="IV")*ISNUMBER(MATCH(B4:B53,{"I","II","III","IV"},0))))/(H4*H4))</f>
         <v/>
       </c>
     </row>
@@ -1743,15 +1778,15 @@
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="13" t="str">
-        <f aca="false">IF(OR(B9="",C9=""),"",IF(B9=C9,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B9="",C9=""),"",IF(AND(ISNUMBER(MATCH(B9,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C9,{"I","II","III","IV"},0))),IF(B9=C9,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E9" s="13" t="str">
-        <f aca="false">IF(OR(B9="",C9=""),"",ABS(MATCH(B9,{"I","II","III","IV"},0)-MATCH(C9,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B9="",C9=""),"",IF(AND(ISNUMBER(MATCH(B9,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C9,{"I","II","III","IV"},0))),ABS(MATCH(B9,{"I","II","III","IV"},0)-MATCH(C9,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G9" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="18" t="str">
         <f aca="false">IF(OR(H4=0,H8=1),"",(H7-H8)/(1-H8))</f>
@@ -1766,15 +1801,15 @@
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="13" t="str">
-        <f aca="false">IF(OR(B10="",C10=""),"",IF(B10=C10,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B10="",C10=""),"",IF(AND(ISNUMBER(MATCH(B10,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C10,{"I","II","III","IV"},0))),IF(B10=C10,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f aca="false">IF(OR(B10="",C10=""),"",ABS(MATCH(B10,{"I","II","III","IV"},0)-MATCH(C10,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B10="",C10=""),"",IF(AND(ISNUMBER(MATCH(B10,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C10,{"I","II","III","IV"},0))),ABS(MATCH(B10,{"I","II","III","IV"},0)-MATCH(C10,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G10" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="13" t="str">
         <f aca="false">IF(H9="","",IF(H9&lt;0.4,"Insuficiente",IF(H9&lt;0.6,"Moderada",IF(H9&lt;0.8,"Substancial","Quase perfeita"))))</f>
@@ -1789,11 +1824,11 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="13" t="str">
-        <f aca="false">IF(OR(B11="",C11=""),"",IF(B11=C11,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B11="",C11=""),"",IF(AND(ISNUMBER(MATCH(B11,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C11,{"I","II","III","IV"},0))),IF(B11=C11,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E11" s="13" t="str">
-        <f aca="false">IF(OR(B11="",C11=""),"",ABS(MATCH(B11,{"I","II","III","IV"},0)-MATCH(C11,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B11="",C11=""),"",IF(AND(ISNUMBER(MATCH(B11,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C11,{"I","II","III","IV"},0))),ABS(MATCH(B11,{"I","II","III","IV"},0)-MATCH(C11,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1805,15 +1840,15 @@
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="13" t="str">
-        <f aca="false">IF(OR(B12="",C12=""),"",IF(B12=C12,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B12="",C12=""),"",IF(AND(ISNUMBER(MATCH(B12,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C12,{"I","II","III","IV"},0))),IF(B12=C12,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f aca="false">IF(OR(B12="",C12=""),"",ABS(MATCH(B12,{"I","II","III","IV"},0)-MATCH(C12,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B12="",C12=""),"",IF(AND(ISNUMBER(MATCH(B12,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C12,{"I","II","III","IV"},0))),ABS(MATCH(B12,{"I","II","III","IV"},0)-MATCH(C12,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
       <c r="G12" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12" s="19"/>
     </row>
@@ -1825,11 +1860,11 @@
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="13" t="str">
-        <f aca="false">IF(OR(B13="",C13=""),"",IF(B13=C13,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B13="",C13=""),"",IF(AND(ISNUMBER(MATCH(B13,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C13,{"I","II","III","IV"},0))),IF(B13=C13,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E13" s="13" t="str">
-        <f aca="false">IF(OR(B13="",C13=""),"",ABS(MATCH(B13,{"I","II","III","IV"},0)-MATCH(C13,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B13="",C13=""),"",IF(AND(ISNUMBER(MATCH(B13,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C13,{"I","II","III","IV"},0))),ABS(MATCH(B13,{"I","II","III","IV"},0)-MATCH(C13,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1841,13 +1876,17 @@
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="13" t="str">
-        <f aca="false">IF(OR(B14="",C14=""),"",IF(B14=C14,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B14="",C14=""),"",IF(AND(ISNUMBER(MATCH(B14,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C14,{"I","II","III","IV"},0))),IF(B14=C14,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f aca="false">IF(OR(B14="",C14=""),"",ABS(MATCH(B14,{"I","II","III","IV"},0)-MATCH(C14,{"I","II","III","IV"},0)))</f>
-        <v/>
-      </c>
+        <f aca="false">IF(OR(B14="",C14=""),"",IF(AND(ISNUMBER(MATCH(B14,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C14,{"I","II","III","IV"},0))),ABS(MATCH(B14,{"I","II","III","IV"},0)-MATCH(C14,{"I","II","III","IV"},0)),""))</f>
+        <v/>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="str">
@@ -1857,12 +1896,19 @@
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="13" t="str">
-        <f aca="false">IF(OR(B15="",C15=""),"",IF(B15=C15,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B15="",C15=""),"",IF(AND(ISNUMBER(MATCH(B15,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C15,{"I","II","III","IV"},0))),IF(B15=C15,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E15" s="13" t="str">
-        <f aca="false">IF(OR(B15="",C15=""),"",ABS(MATCH(B15,{"I","II","III","IV"},0)-MATCH(C15,{"I","II","III","IV"},0)))</f>
-        <v/>
+        <f aca="false">IF(OR(B15="",C15=""),"",IF(AND(ISNUMBER(MATCH(B15,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C15,{"I","II","III","IV"},0))),ABS(MATCH(B15,{"I","II","III","IV"},0)-MATCH(C15,{"I","II","III","IV"},0)),""))</f>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <f aca="false">COUNTIFS(B4:B53,"&lt;&gt;",C4:C53,"&lt;&gt;")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1873,12 +1919,19 @@
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="13" t="str">
-        <f aca="false">IF(OR(B16="",C16=""),"",IF(B16=C16,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B16="",C16=""),"",IF(AND(ISNUMBER(MATCH(B16,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C16,{"I","II","III","IV"},0))),IF(B16=C16,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f aca="false">IF(OR(B16="",C16=""),"",ABS(MATCH(B16,{"I","II","III","IV"},0)-MATCH(C16,{"I","II","III","IV"},0)))</f>
-        <v/>
+        <f aca="false">IF(OR(B16="",C16=""),"",IF(AND(ISNUMBER(MATCH(B16,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C16,{"I","II","III","IV"},0))),ABS(MATCH(B16,{"I","II","III","IV"},0)-MATCH(C16,{"I","II","III","IV"},0)),""))</f>
+        <v/>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <f aca="false">IF(H15="","",H15-H4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1889,11 +1942,18 @@
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="13" t="str">
-        <f aca="false">IF(OR(B17="",C17=""),"",IF(B17=C17,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B17="",C17=""),"",IF(AND(ISNUMBER(MATCH(B17,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C17,{"I","II","III","IV"},0))),IF(B17=C17,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E17" s="13" t="str">
-        <f aca="false">IF(OR(B17="",C17=""),"",ABS(MATCH(B17,{"I","II","III","IV"},0)-MATCH(C17,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B17="",C17=""),"",IF(AND(ISNUMBER(MATCH(B17,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C17,{"I","II","III","IV"},0))),ABS(MATCH(B17,{"I","II","III","IV"},0)-MATCH(C17,{"I","II","III","IV"},0)),""))</f>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="23" t="str">
+        <f aca="false">IF(H15=0,"",(H4+COUNTIFS(B4:B53,"NÃO AVALIÁVEL",C4:C53,"NÃO AVALIÁVEL"))/H15)</f>
         <v/>
       </c>
     </row>
@@ -1905,11 +1965,11 @@
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="13" t="str">
-        <f aca="false">IF(OR(B18="",C18=""),"",IF(B18=C18,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B18="",C18=""),"",IF(AND(ISNUMBER(MATCH(B18,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C18,{"I","II","III","IV"},0))),IF(B18=C18,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f aca="false">IF(OR(B18="",C18=""),"",ABS(MATCH(B18,{"I","II","III","IV"},0)-MATCH(C18,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B18="",C18=""),"",IF(AND(ISNUMBER(MATCH(B18,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C18,{"I","II","III","IV"},0))),ABS(MATCH(B18,{"I","II","III","IV"},0)-MATCH(C18,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1921,11 +1981,11 @@
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="13" t="str">
-        <f aca="false">IF(OR(B19="",C19=""),"",IF(B19=C19,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B19="",C19=""),"",IF(AND(ISNUMBER(MATCH(B19,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C19,{"I","II","III","IV"},0))),IF(B19=C19,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E19" s="13" t="str">
-        <f aca="false">IF(OR(B19="",C19=""),"",ABS(MATCH(B19,{"I","II","III","IV"},0)-MATCH(C19,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B19="",C19=""),"",IF(AND(ISNUMBER(MATCH(B19,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C19,{"I","II","III","IV"},0))),ABS(MATCH(B19,{"I","II","III","IV"},0)-MATCH(C19,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1937,11 +1997,11 @@
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="13" t="str">
-        <f aca="false">IF(OR(B20="",C20=""),"",IF(B20=C20,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B20="",C20=""),"",IF(AND(ISNUMBER(MATCH(B20,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C20,{"I","II","III","IV"},0))),IF(B20=C20,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E20" s="13" t="str">
-        <f aca="false">IF(OR(B20="",C20=""),"",ABS(MATCH(B20,{"I","II","III","IV"},0)-MATCH(C20,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B20="",C20=""),"",IF(AND(ISNUMBER(MATCH(B20,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C20,{"I","II","III","IV"},0))),ABS(MATCH(B20,{"I","II","III","IV"},0)-MATCH(C20,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1953,11 +2013,11 @@
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="13" t="str">
-        <f aca="false">IF(OR(B21="",C21=""),"",IF(B21=C21,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B21="",C21=""),"",IF(AND(ISNUMBER(MATCH(B21,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C21,{"I","II","III","IV"},0))),IF(B21=C21,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E21" s="13" t="str">
-        <f aca="false">IF(OR(B21="",C21=""),"",ABS(MATCH(B21,{"I","II","III","IV"},0)-MATCH(C21,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B21="",C21=""),"",IF(AND(ISNUMBER(MATCH(B21,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C21,{"I","II","III","IV"},0))),ABS(MATCH(B21,{"I","II","III","IV"},0)-MATCH(C21,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1969,11 +2029,11 @@
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="13" t="str">
-        <f aca="false">IF(OR(B22="",C22=""),"",IF(B22=C22,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B22="",C22=""),"",IF(AND(ISNUMBER(MATCH(B22,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C22,{"I","II","III","IV"},0))),IF(B22=C22,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E22" s="13" t="str">
-        <f aca="false">IF(OR(B22="",C22=""),"",ABS(MATCH(B22,{"I","II","III","IV"},0)-MATCH(C22,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B22="",C22=""),"",IF(AND(ISNUMBER(MATCH(B22,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C22,{"I","II","III","IV"},0))),ABS(MATCH(B22,{"I","II","III","IV"},0)-MATCH(C22,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -1985,11 +2045,11 @@
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="13" t="str">
-        <f aca="false">IF(OR(B23="",C23=""),"",IF(B23=C23,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B23="",C23=""),"",IF(AND(ISNUMBER(MATCH(B23,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C23,{"I","II","III","IV"},0))),IF(B23=C23,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E23" s="13" t="str">
-        <f aca="false">IF(OR(B23="",C23=""),"",ABS(MATCH(B23,{"I","II","III","IV"},0)-MATCH(C23,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B23="",C23=""),"",IF(AND(ISNUMBER(MATCH(B23,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C23,{"I","II","III","IV"},0))),ABS(MATCH(B23,{"I","II","III","IV"},0)-MATCH(C23,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2001,11 +2061,11 @@
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="13" t="str">
-        <f aca="false">IF(OR(B24="",C24=""),"",IF(B24=C24,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B24="",C24=""),"",IF(AND(ISNUMBER(MATCH(B24,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C24,{"I","II","III","IV"},0))),IF(B24=C24,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E24" s="13" t="str">
-        <f aca="false">IF(OR(B24="",C24=""),"",ABS(MATCH(B24,{"I","II","III","IV"},0)-MATCH(C24,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B24="",C24=""),"",IF(AND(ISNUMBER(MATCH(B24,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C24,{"I","II","III","IV"},0))),ABS(MATCH(B24,{"I","II","III","IV"},0)-MATCH(C24,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2017,11 +2077,11 @@
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="13" t="str">
-        <f aca="false">IF(OR(B25="",C25=""),"",IF(B25=C25,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B25="",C25=""),"",IF(AND(ISNUMBER(MATCH(B25,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C25,{"I","II","III","IV"},0))),IF(B25=C25,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E25" s="13" t="str">
-        <f aca="false">IF(OR(B25="",C25=""),"",ABS(MATCH(B25,{"I","II","III","IV"},0)-MATCH(C25,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B25="",C25=""),"",IF(AND(ISNUMBER(MATCH(B25,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C25,{"I","II","III","IV"},0))),ABS(MATCH(B25,{"I","II","III","IV"},0)-MATCH(C25,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2033,11 +2093,11 @@
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="13" t="str">
-        <f aca="false">IF(OR(B26="",C26=""),"",IF(B26=C26,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B26="",C26=""),"",IF(AND(ISNUMBER(MATCH(B26,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C26,{"I","II","III","IV"},0))),IF(B26=C26,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E26" s="13" t="str">
-        <f aca="false">IF(OR(B26="",C26=""),"",ABS(MATCH(B26,{"I","II","III","IV"},0)-MATCH(C26,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B26="",C26=""),"",IF(AND(ISNUMBER(MATCH(B26,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C26,{"I","II","III","IV"},0))),ABS(MATCH(B26,{"I","II","III","IV"},0)-MATCH(C26,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2049,11 +2109,11 @@
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="13" t="str">
-        <f aca="false">IF(OR(B27="",C27=""),"",IF(B27=C27,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B27="",C27=""),"",IF(AND(ISNUMBER(MATCH(B27,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C27,{"I","II","III","IV"},0))),IF(B27=C27,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E27" s="13" t="str">
-        <f aca="false">IF(OR(B27="",C27=""),"",ABS(MATCH(B27,{"I","II","III","IV"},0)-MATCH(C27,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B27="",C27=""),"",IF(AND(ISNUMBER(MATCH(B27,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C27,{"I","II","III","IV"},0))),ABS(MATCH(B27,{"I","II","III","IV"},0)-MATCH(C27,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2065,11 +2125,11 @@
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="13" t="str">
-        <f aca="false">IF(OR(B28="",C28=""),"",IF(B28=C28,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B28="",C28=""),"",IF(AND(ISNUMBER(MATCH(B28,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C28,{"I","II","III","IV"},0))),IF(B28=C28,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E28" s="13" t="str">
-        <f aca="false">IF(OR(B28="",C28=""),"",ABS(MATCH(B28,{"I","II","III","IV"},0)-MATCH(C28,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B28="",C28=""),"",IF(AND(ISNUMBER(MATCH(B28,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C28,{"I","II","III","IV"},0))),ABS(MATCH(B28,{"I","II","III","IV"},0)-MATCH(C28,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2081,11 +2141,11 @@
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="13" t="str">
-        <f aca="false">IF(OR(B29="",C29=""),"",IF(B29=C29,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B29="",C29=""),"",IF(AND(ISNUMBER(MATCH(B29,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C29,{"I","II","III","IV"},0))),IF(B29=C29,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E29" s="13" t="str">
-        <f aca="false">IF(OR(B29="",C29=""),"",ABS(MATCH(B29,{"I","II","III","IV"},0)-MATCH(C29,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B29="",C29=""),"",IF(AND(ISNUMBER(MATCH(B29,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C29,{"I","II","III","IV"},0))),ABS(MATCH(B29,{"I","II","III","IV"},0)-MATCH(C29,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2097,11 +2157,11 @@
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="13" t="str">
-        <f aca="false">IF(OR(B30="",C30=""),"",IF(B30=C30,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B30="",C30=""),"",IF(AND(ISNUMBER(MATCH(B30,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C30,{"I","II","III","IV"},0))),IF(B30=C30,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E30" s="13" t="str">
-        <f aca="false">IF(OR(B30="",C30=""),"",ABS(MATCH(B30,{"I","II","III","IV"},0)-MATCH(C30,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B30="",C30=""),"",IF(AND(ISNUMBER(MATCH(B30,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C30,{"I","II","III","IV"},0))),ABS(MATCH(B30,{"I","II","III","IV"},0)-MATCH(C30,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2113,11 +2173,11 @@
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="13" t="str">
-        <f aca="false">IF(OR(B31="",C31=""),"",IF(B31=C31,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B31="",C31=""),"",IF(AND(ISNUMBER(MATCH(B31,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C31,{"I","II","III","IV"},0))),IF(B31=C31,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E31" s="13" t="str">
-        <f aca="false">IF(OR(B31="",C31=""),"",ABS(MATCH(B31,{"I","II","III","IV"},0)-MATCH(C31,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B31="",C31=""),"",IF(AND(ISNUMBER(MATCH(B31,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C31,{"I","II","III","IV"},0))),ABS(MATCH(B31,{"I","II","III","IV"},0)-MATCH(C31,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2129,11 +2189,11 @@
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="13" t="str">
-        <f aca="false">IF(OR(B32="",C32=""),"",IF(B32=C32,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B32="",C32=""),"",IF(AND(ISNUMBER(MATCH(B32,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C32,{"I","II","III","IV"},0))),IF(B32=C32,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E32" s="13" t="str">
-        <f aca="false">IF(OR(B32="",C32=""),"",ABS(MATCH(B32,{"I","II","III","IV"},0)-MATCH(C32,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B32="",C32=""),"",IF(AND(ISNUMBER(MATCH(B32,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C32,{"I","II","III","IV"},0))),ABS(MATCH(B32,{"I","II","III","IV"},0)-MATCH(C32,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2145,11 +2205,11 @@
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="13" t="str">
-        <f aca="false">IF(OR(B33="",C33=""),"",IF(B33=C33,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B33="",C33=""),"",IF(AND(ISNUMBER(MATCH(B33,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C33,{"I","II","III","IV"},0))),IF(B33=C33,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E33" s="13" t="str">
-        <f aca="false">IF(OR(B33="",C33=""),"",ABS(MATCH(B33,{"I","II","III","IV"},0)-MATCH(C33,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B33="",C33=""),"",IF(AND(ISNUMBER(MATCH(B33,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C33,{"I","II","III","IV"},0))),ABS(MATCH(B33,{"I","II","III","IV"},0)-MATCH(C33,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2161,11 +2221,11 @@
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
       <c r="D34" s="13" t="str">
-        <f aca="false">IF(OR(B34="",C34=""),"",IF(B34=C34,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B34="",C34=""),"",IF(AND(ISNUMBER(MATCH(B34,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C34,{"I","II","III","IV"},0))),IF(B34=C34,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E34" s="13" t="str">
-        <f aca="false">IF(OR(B34="",C34=""),"",ABS(MATCH(B34,{"I","II","III","IV"},0)-MATCH(C34,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B34="",C34=""),"",IF(AND(ISNUMBER(MATCH(B34,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C34,{"I","II","III","IV"},0))),ABS(MATCH(B34,{"I","II","III","IV"},0)-MATCH(C34,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2177,11 +2237,11 @@
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="13" t="str">
-        <f aca="false">IF(OR(B35="",C35=""),"",IF(B35=C35,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B35="",C35=""),"",IF(AND(ISNUMBER(MATCH(B35,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C35,{"I","II","III","IV"},0))),IF(B35=C35,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E35" s="13" t="str">
-        <f aca="false">IF(OR(B35="",C35=""),"",ABS(MATCH(B35,{"I","II","III","IV"},0)-MATCH(C35,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B35="",C35=""),"",IF(AND(ISNUMBER(MATCH(B35,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C35,{"I","II","III","IV"},0))),ABS(MATCH(B35,{"I","II","III","IV"},0)-MATCH(C35,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2193,11 +2253,11 @@
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="13" t="str">
-        <f aca="false">IF(OR(B36="",C36=""),"",IF(B36=C36,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B36="",C36=""),"",IF(AND(ISNUMBER(MATCH(B36,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C36,{"I","II","III","IV"},0))),IF(B36=C36,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E36" s="13" t="str">
-        <f aca="false">IF(OR(B36="",C36=""),"",ABS(MATCH(B36,{"I","II","III","IV"},0)-MATCH(C36,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B36="",C36=""),"",IF(AND(ISNUMBER(MATCH(B36,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C36,{"I","II","III","IV"},0))),ABS(MATCH(B36,{"I","II","III","IV"},0)-MATCH(C36,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2209,11 +2269,11 @@
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="13" t="str">
-        <f aca="false">IF(OR(B37="",C37=""),"",IF(B37=C37,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B37="",C37=""),"",IF(AND(ISNUMBER(MATCH(B37,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C37,{"I","II","III","IV"},0))),IF(B37=C37,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E37" s="13" t="str">
-        <f aca="false">IF(OR(B37="",C37=""),"",ABS(MATCH(B37,{"I","II","III","IV"},0)-MATCH(C37,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B37="",C37=""),"",IF(AND(ISNUMBER(MATCH(B37,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C37,{"I","II","III","IV"},0))),ABS(MATCH(B37,{"I","II","III","IV"},0)-MATCH(C37,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2225,11 +2285,11 @@
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="13" t="str">
-        <f aca="false">IF(OR(B38="",C38=""),"",IF(B38=C38,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B38="",C38=""),"",IF(AND(ISNUMBER(MATCH(B38,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C38,{"I","II","III","IV"},0))),IF(B38=C38,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E38" s="13" t="str">
-        <f aca="false">IF(OR(B38="",C38=""),"",ABS(MATCH(B38,{"I","II","III","IV"},0)-MATCH(C38,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B38="",C38=""),"",IF(AND(ISNUMBER(MATCH(B38,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C38,{"I","II","III","IV"},0))),ABS(MATCH(B38,{"I","II","III","IV"},0)-MATCH(C38,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2241,11 +2301,11 @@
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="13" t="str">
-        <f aca="false">IF(OR(B39="",C39=""),"",IF(B39=C39,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B39="",C39=""),"",IF(AND(ISNUMBER(MATCH(B39,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C39,{"I","II","III","IV"},0))),IF(B39=C39,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E39" s="13" t="str">
-        <f aca="false">IF(OR(B39="",C39=""),"",ABS(MATCH(B39,{"I","II","III","IV"},0)-MATCH(C39,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B39="",C39=""),"",IF(AND(ISNUMBER(MATCH(B39,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C39,{"I","II","III","IV"},0))),ABS(MATCH(B39,{"I","II","III","IV"},0)-MATCH(C39,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2257,11 +2317,11 @@
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="D40" s="13" t="str">
-        <f aca="false">IF(OR(B40="",C40=""),"",IF(B40=C40,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B40="",C40=""),"",IF(AND(ISNUMBER(MATCH(B40,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C40,{"I","II","III","IV"},0))),IF(B40=C40,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E40" s="13" t="str">
-        <f aca="false">IF(OR(B40="",C40=""),"",ABS(MATCH(B40,{"I","II","III","IV"},0)-MATCH(C40,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B40="",C40=""),"",IF(AND(ISNUMBER(MATCH(B40,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C40,{"I","II","III","IV"},0))),ABS(MATCH(B40,{"I","II","III","IV"},0)-MATCH(C40,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2273,11 +2333,11 @@
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="13" t="str">
-        <f aca="false">IF(OR(B41="",C41=""),"",IF(B41=C41,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B41="",C41=""),"",IF(AND(ISNUMBER(MATCH(B41,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C41,{"I","II","III","IV"},0))),IF(B41=C41,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E41" s="13" t="str">
-        <f aca="false">IF(OR(B41="",C41=""),"",ABS(MATCH(B41,{"I","II","III","IV"},0)-MATCH(C41,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B41="",C41=""),"",IF(AND(ISNUMBER(MATCH(B41,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C41,{"I","II","III","IV"},0))),ABS(MATCH(B41,{"I","II","III","IV"},0)-MATCH(C41,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2289,11 +2349,11 @@
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="13" t="str">
-        <f aca="false">IF(OR(B42="",C42=""),"",IF(B42=C42,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B42="",C42=""),"",IF(AND(ISNUMBER(MATCH(B42,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C42,{"I","II","III","IV"},0))),IF(B42=C42,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E42" s="13" t="str">
-        <f aca="false">IF(OR(B42="",C42=""),"",ABS(MATCH(B42,{"I","II","III","IV"},0)-MATCH(C42,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B42="",C42=""),"",IF(AND(ISNUMBER(MATCH(B42,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C42,{"I","II","III","IV"},0))),ABS(MATCH(B42,{"I","II","III","IV"},0)-MATCH(C42,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2305,11 +2365,11 @@
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="13" t="str">
-        <f aca="false">IF(OR(B43="",C43=""),"",IF(B43=C43,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B43="",C43=""),"",IF(AND(ISNUMBER(MATCH(B43,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C43,{"I","II","III","IV"},0))),IF(B43=C43,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E43" s="13" t="str">
-        <f aca="false">IF(OR(B43="",C43=""),"",ABS(MATCH(B43,{"I","II","III","IV"},0)-MATCH(C43,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B43="",C43=""),"",IF(AND(ISNUMBER(MATCH(B43,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C43,{"I","II","III","IV"},0))),ABS(MATCH(B43,{"I","II","III","IV"},0)-MATCH(C43,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2321,11 +2381,11 @@
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
       <c r="D44" s="13" t="str">
-        <f aca="false">IF(OR(B44="",C44=""),"",IF(B44=C44,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B44="",C44=""),"",IF(AND(ISNUMBER(MATCH(B44,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C44,{"I","II","III","IV"},0))),IF(B44=C44,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E44" s="13" t="str">
-        <f aca="false">IF(OR(B44="",C44=""),"",ABS(MATCH(B44,{"I","II","III","IV"},0)-MATCH(C44,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B44="",C44=""),"",IF(AND(ISNUMBER(MATCH(B44,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C44,{"I","II","III","IV"},0))),ABS(MATCH(B44,{"I","II","III","IV"},0)-MATCH(C44,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2337,11 +2397,11 @@
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
       <c r="D45" s="13" t="str">
-        <f aca="false">IF(OR(B45="",C45=""),"",IF(B45=C45,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B45="",C45=""),"",IF(AND(ISNUMBER(MATCH(B45,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C45,{"I","II","III","IV"},0))),IF(B45=C45,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E45" s="13" t="str">
-        <f aca="false">IF(OR(B45="",C45=""),"",ABS(MATCH(B45,{"I","II","III","IV"},0)-MATCH(C45,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B45="",C45=""),"",IF(AND(ISNUMBER(MATCH(B45,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C45,{"I","II","III","IV"},0))),ABS(MATCH(B45,{"I","II","III","IV"},0)-MATCH(C45,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2353,11 +2413,11 @@
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="13" t="str">
-        <f aca="false">IF(OR(B46="",C46=""),"",IF(B46=C46,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B46="",C46=""),"",IF(AND(ISNUMBER(MATCH(B46,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C46,{"I","II","III","IV"},0))),IF(B46=C46,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E46" s="13" t="str">
-        <f aca="false">IF(OR(B46="",C46=""),"",ABS(MATCH(B46,{"I","II","III","IV"},0)-MATCH(C46,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B46="",C46=""),"",IF(AND(ISNUMBER(MATCH(B46,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C46,{"I","II","III","IV"},0))),ABS(MATCH(B46,{"I","II","III","IV"},0)-MATCH(C46,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2369,11 +2429,11 @@
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
       <c r="D47" s="13" t="str">
-        <f aca="false">IF(OR(B47="",C47=""),"",IF(B47=C47,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B47="",C47=""),"",IF(AND(ISNUMBER(MATCH(B47,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C47,{"I","II","III","IV"},0))),IF(B47=C47,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E47" s="13" t="str">
-        <f aca="false">IF(OR(B47="",C47=""),"",ABS(MATCH(B47,{"I","II","III","IV"},0)-MATCH(C47,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B47="",C47=""),"",IF(AND(ISNUMBER(MATCH(B47,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C47,{"I","II","III","IV"},0))),ABS(MATCH(B47,{"I","II","III","IV"},0)-MATCH(C47,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2385,11 +2445,11 @@
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="13" t="str">
-        <f aca="false">IF(OR(B48="",C48=""),"",IF(B48=C48,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B48="",C48=""),"",IF(AND(ISNUMBER(MATCH(B48,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C48,{"I","II","III","IV"},0))),IF(B48=C48,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E48" s="13" t="str">
-        <f aca="false">IF(OR(B48="",C48=""),"",ABS(MATCH(B48,{"I","II","III","IV"},0)-MATCH(C48,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B48="",C48=""),"",IF(AND(ISNUMBER(MATCH(B48,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C48,{"I","II","III","IV"},0))),ABS(MATCH(B48,{"I","II","III","IV"},0)-MATCH(C48,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2401,11 +2461,11 @@
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="13" t="str">
-        <f aca="false">IF(OR(B49="",C49=""),"",IF(B49=C49,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B49="",C49=""),"",IF(AND(ISNUMBER(MATCH(B49,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C49,{"I","II","III","IV"},0))),IF(B49=C49,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E49" s="13" t="str">
-        <f aca="false">IF(OR(B49="",C49=""),"",ABS(MATCH(B49,{"I","II","III","IV"},0)-MATCH(C49,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B49="",C49=""),"",IF(AND(ISNUMBER(MATCH(B49,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C49,{"I","II","III","IV"},0))),ABS(MATCH(B49,{"I","II","III","IV"},0)-MATCH(C49,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2417,11 +2477,11 @@
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="13" t="str">
-        <f aca="false">IF(OR(B50="",C50=""),"",IF(B50=C50,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B50="",C50=""),"",IF(AND(ISNUMBER(MATCH(B50,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C50,{"I","II","III","IV"},0))),IF(B50=C50,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E50" s="13" t="str">
-        <f aca="false">IF(OR(B50="",C50=""),"",ABS(MATCH(B50,{"I","II","III","IV"},0)-MATCH(C50,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B50="",C50=""),"",IF(AND(ISNUMBER(MATCH(B50,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C50,{"I","II","III","IV"},0))),ABS(MATCH(B50,{"I","II","III","IV"},0)-MATCH(C50,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2433,11 +2493,11 @@
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="13" t="str">
-        <f aca="false">IF(OR(B51="",C51=""),"",IF(B51=C51,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B51="",C51=""),"",IF(AND(ISNUMBER(MATCH(B51,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C51,{"I","II","III","IV"},0))),IF(B51=C51,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E51" s="13" t="str">
-        <f aca="false">IF(OR(B51="",C51=""),"",ABS(MATCH(B51,{"I","II","III","IV"},0)-MATCH(C51,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B51="",C51=""),"",IF(AND(ISNUMBER(MATCH(B51,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C51,{"I","II","III","IV"},0))),ABS(MATCH(B51,{"I","II","III","IV"},0)-MATCH(C51,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2449,11 +2509,11 @@
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="13" t="str">
-        <f aca="false">IF(OR(B52="",C52=""),"",IF(B52=C52,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B52="",C52=""),"",IF(AND(ISNUMBER(MATCH(B52,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C52,{"I","II","III","IV"},0))),IF(B52=C52,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E52" s="13" t="str">
-        <f aca="false">IF(OR(B52="",C52=""),"",ABS(MATCH(B52,{"I","II","III","IV"},0)-MATCH(C52,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B52="",C52=""),"",IF(AND(ISNUMBER(MATCH(B52,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C52,{"I","II","III","IV"},0))),ABS(MATCH(B52,{"I","II","III","IV"},0)-MATCH(C52,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
@@ -2465,21 +2525,28 @@
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="13" t="str">
-        <f aca="false">IF(OR(B53="",C53=""),"",IF(B53=C53,"Sim","Não"))</f>
+        <f aca="false">IF(OR(B53="",C53=""),"",IF(AND(ISNUMBER(MATCH(B53,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C53,{"I","II","III","IV"},0))),IF(B53=C53,"Sim","Não"),""))</f>
         <v/>
       </c>
       <c r="E53" s="13" t="str">
-        <f aca="false">IF(OR(B53="",C53=""),"",ABS(MATCH(B53,{"I","II","III","IV"},0)-MATCH(C53,{"I","II","III","IV"},0)))</f>
+        <f aca="false">IF(OR(B53="",C53=""),"",IF(AND(ISNUMBER(MATCH(B53,{"I","II","III","IV"},0)),ISNUMBER(MATCH(C53,{"I","II","III","IV"},0))),ABS(MATCH(B53,{"I","II","III","IV"},0)-MATCH(C53,{"I","II","III","IV"},0)),""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G14:H14"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Use I, II, III, IV ou NÃO AVALIÁVEL." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4:C53" type="list">
+      <formula1>"I,II,III,IV,NÃO AVALIÁVEL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2502,16 +2569,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2526,1872 +2593,1576 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
+      <c r="A2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="A3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="C3" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="D3" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="E3" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="F3" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="G3" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="H3" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="I3" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="20"/>
-      <c r="P3" s="22" t="s">
+      <c r="J3" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
+      <c r="K3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="str">
+      <c r="A4" s="26" t="str">
         <f aca="false">IF(Protocolos!A4="","",Protocolos!A4)</f>
         <v/>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="23" t="str">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="26" t="str">
         <f aca="false">IF(L4="Sim","",IF(COUNT(B4:I4)=0,"",MAX(0,SUM(B4:I4))))</f>
         <v/>
       </c>
-      <c r="N4" s="23" t="str">
+      <c r="N4" s="26" t="str">
         <f aca="false">IF(L4="Sim","NÃO AVALIÁVEL",IF(M4="","",IF(K4="Sim","IV",IF(J4="Sim",IF(M4&lt;=64,"I",IF(M4&lt;=141,"II",IF(M4&lt;=230,"III","IV"))),IF(M4&lt;=58,"I",IF(M4&lt;=127,"II",IF(M4&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O4" s="25"/>
-      <c r="P4" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="26" t="str">
         <f aca="false">IF(Protocolos!A5="","",Protocolos!A5)</f>
         <v/>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="23" t="str">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="26" t="str">
         <f aca="false">IF(L5="Sim","",IF(COUNT(B5:I5)=0,"",MAX(0,SUM(B5:I5))))</f>
         <v/>
       </c>
-      <c r="N5" s="23" t="str">
+      <c r="N5" s="26" t="str">
         <f aca="false">IF(L5="Sim","NÃO AVALIÁVEL",IF(M5="","",IF(K5="Sim","IV",IF(J5="Sim",IF(M5&lt;=64,"I",IF(M5&lt;=141,"II",IF(M5&lt;=230,"III","IV"))),IF(M5&lt;=58,"I",IF(M5&lt;=127,"II",IF(M5&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O5" s="26"/>
-      <c r="P5" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q5" s="23" t="n">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" s="26" t="n">
         <f aca="false">COUNTIF(N4:N53,"I")</f>
         <v>0</v>
       </c>
-      <c r="R5" s="28" t="str">
+      <c r="R5" s="31" t="str">
         <f aca="false">IF(SUM(Q5:Q8)=0,"",Q5/SUM(Q5:Q8))</f>
         <v/>
       </c>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="str">
+      <c r="A6" s="26" t="str">
         <f aca="false">IF(Protocolos!A6="","",Protocolos!A6)</f>
         <v/>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="23" t="str">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="26" t="str">
         <f aca="false">IF(L6="Sim","",IF(COUNT(B6:I6)=0,"",MAX(0,SUM(B6:I6))))</f>
         <v/>
       </c>
-      <c r="N6" s="23" t="str">
+      <c r="N6" s="26" t="str">
         <f aca="false">IF(L6="Sim","NÃO AVALIÁVEL",IF(M6="","",IF(K6="Sim","IV",IF(J6="Sim",IF(M6&lt;=64,"I",IF(M6&lt;=141,"II",IF(M6&lt;=230,"III","IV"))),IF(M6&lt;=58,"I",IF(M6&lt;=127,"II",IF(M6&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q6" s="23" t="n">
+      <c r="O6" s="29"/>
+      <c r="P6" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" s="26" t="n">
         <f aca="false">COUNTIF(N4:N53,"II")</f>
         <v>0</v>
       </c>
-      <c r="R6" s="28" t="str">
+      <c r="R6" s="31" t="str">
         <f aca="false">IF(SUM(Q5:Q8)=0,"",Q6/SUM(Q5:Q8))</f>
         <v/>
       </c>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="str">
+      <c r="A7" s="26" t="str">
         <f aca="false">IF(Protocolos!A7="","",Protocolos!A7)</f>
         <v/>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="23" t="str">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="26" t="str">
         <f aca="false">IF(L7="Sim","",IF(COUNT(B7:I7)=0,"",MAX(0,SUM(B7:I7))))</f>
         <v/>
       </c>
-      <c r="N7" s="23" t="str">
+      <c r="N7" s="26" t="str">
         <f aca="false">IF(L7="Sim","NÃO AVALIÁVEL",IF(M7="","",IF(K7="Sim","IV",IF(J7="Sim",IF(M7&lt;=64,"I",IF(M7&lt;=141,"II",IF(M7&lt;=230,"III","IV"))),IF(M7&lt;=58,"I",IF(M7&lt;=127,"II",IF(M7&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" s="23" t="n">
+      <c r="O7" s="29"/>
+      <c r="P7" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="26" t="n">
         <f aca="false">COUNTIF(N4:N53,"III")</f>
         <v>0</v>
       </c>
-      <c r="R7" s="28" t="str">
+      <c r="R7" s="31" t="str">
         <f aca="false">IF(SUM(Q5:Q8)=0,"",Q7/SUM(Q5:Q8))</f>
         <v/>
       </c>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="str">
+      <c r="A8" s="26" t="str">
         <f aca="false">IF(Protocolos!A8="","",Protocolos!A8)</f>
         <v/>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="23" t="str">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="26" t="str">
         <f aca="false">IF(L8="Sim","",IF(COUNT(B8:I8)=0,"",MAX(0,SUM(B8:I8))))</f>
         <v/>
       </c>
-      <c r="N8" s="23" t="str">
+      <c r="N8" s="26" t="str">
         <f aca="false">IF(L8="Sim","NÃO AVALIÁVEL",IF(M8="","",IF(K8="Sim","IV",IF(J8="Sim",IF(M8&lt;=64,"I",IF(M8&lt;=141,"II",IF(M8&lt;=230,"III","IV"))),IF(M8&lt;=58,"I",IF(M8&lt;=127,"II",IF(M8&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q8" s="23" t="n">
+      <c r="O8" s="29"/>
+      <c r="P8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" s="26" t="n">
         <f aca="false">COUNTIF(N4:N53,"IV")</f>
         <v>0</v>
       </c>
-      <c r="R8" s="28" t="str">
+      <c r="R8" s="31" t="str">
         <f aca="false">IF(SUM(Q5:Q8)=0,"",Q8/SUM(Q5:Q8))</f>
         <v/>
       </c>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="str">
+      <c r="A9" s="26" t="str">
         <f aca="false">IF(Protocolos!A9="","",Protocolos!A9)</f>
         <v/>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="23" t="str">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="26" t="str">
         <f aca="false">IF(L9="Sim","",IF(COUNT(B9:I9)=0,"",MAX(0,SUM(B9:I9))))</f>
         <v/>
       </c>
-      <c r="N9" s="23" t="str">
+      <c r="N9" s="26" t="str">
         <f aca="false">IF(L9="Sim","NÃO AVALIÁVEL",IF(M9="","",IF(K9="Sim","IV",IF(J9="Sim",IF(M9&lt;=64,"I",IF(M9&lt;=141,"II",IF(M9&lt;=230,"III","IV"))),IF(M9&lt;=58,"I",IF(M9&lt;=127,"II",IF(M9&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="23" t="n">
+      <c r="P9" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="26" t="n">
         <f aca="false">SUM(Q5:Q8)</f>
         <v>0</v>
       </c>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="26" t="str">
         <f aca="false">IF(Protocolos!A10="","",Protocolos!A10)</f>
         <v/>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="23" t="str">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="26" t="str">
         <f aca="false">IF(L10="Sim","",IF(COUNT(B10:I10)=0,"",MAX(0,SUM(B10:I10))))</f>
         <v/>
       </c>
-      <c r="N10" s="23" t="str">
+      <c r="N10" s="26" t="str">
         <f aca="false">IF(L10="Sim","NÃO AVALIÁVEL",IF(M10="","",IF(K10="Sim","IV",IF(J10="Sim",IF(M10&lt;=64,"I",IF(M10&lt;=141,"II",IF(M10&lt;=230,"III","IV"))),IF(M10&lt;=58,"I",IF(M10&lt;=127,"II",IF(M10&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O10" s="20"/>
-      <c r="P10" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q10" s="23" t="n">
+      <c r="P10" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="26" t="n">
         <f aca="false">COUNTIF(N4:N53,"NÃO AVALIÁVEL")</f>
         <v>0</v>
       </c>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="str">
+      <c r="A11" s="26" t="str">
         <f aca="false">IF(Protocolos!A11="","",Protocolos!A11)</f>
         <v/>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="23" t="str">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="26" t="str">
         <f aca="false">IF(L11="Sim","",IF(COUNT(B11:I11)=0,"",MAX(0,SUM(B11:I11))))</f>
         <v/>
       </c>
-      <c r="N11" s="23" t="str">
+      <c r="N11" s="26" t="str">
         <f aca="false">IF(L11="Sim","NÃO AVALIÁVEL",IF(M11="","",IF(K11="Sim","IV",IF(J11="Sim",IF(M11&lt;=64,"I",IF(M11&lt;=141,"II",IF(M11&lt;=230,"III","IV"))),IF(M11&lt;=58,"I",IF(M11&lt;=127,"II",IF(M11&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O11" s="20"/>
-      <c r="P11" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="23" t="n">
+      <c r="P11" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q11" s="26" t="n">
         <f aca="false">COUNTIFS(K4:K53,"Sim",N4:N53,"IV")</f>
         <v>0</v>
       </c>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="str">
+      <c r="A12" s="26" t="str">
         <f aca="false">IF(Protocolos!A12="","",Protocolos!A12)</f>
         <v/>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="23" t="str">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="26" t="str">
         <f aca="false">IF(L12="Sim","",IF(COUNT(B12:I12)=0,"",MAX(0,SUM(B12:I12))))</f>
         <v/>
       </c>
-      <c r="N12" s="23" t="str">
+      <c r="N12" s="26" t="str">
         <f aca="false">IF(L12="Sim","NÃO AVALIÁVEL",IF(M12="","",IF(K12="Sim","IV",IF(J12="Sim",IF(M12&lt;=64,"I",IF(M12&lt;=141,"II",IF(M12&lt;=230,"III","IV"))),IF(M12&lt;=58,"I",IF(M12&lt;=127,"II",IF(M12&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="str">
+      <c r="A13" s="26" t="str">
         <f aca="false">IF(Protocolos!A13="","",Protocolos!A13)</f>
         <v/>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="23" t="str">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="26" t="str">
         <f aca="false">IF(L13="Sim","",IF(COUNT(B13:I13)=0,"",MAX(0,SUM(B13:I13))))</f>
         <v/>
       </c>
-      <c r="N13" s="23" t="str">
+      <c r="N13" s="26" t="str">
         <f aca="false">IF(L13="Sim","NÃO AVALIÁVEL",IF(M13="","",IF(K13="Sim","IV",IF(J13="Sim",IF(M13&lt;=64,"I",IF(M13&lt;=141,"II",IF(M13&lt;=230,"III","IV"))),IF(M13&lt;=58,"I",IF(M13&lt;=127,"II",IF(M13&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O13" s="20"/>
-      <c r="P13" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
+      <c r="P13" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="str">
+      <c r="A14" s="26" t="str">
         <f aca="false">IF(Protocolos!A14="","",Protocolos!A14)</f>
         <v/>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="23" t="str">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="26" t="str">
         <f aca="false">IF(L14="Sim","",IF(COUNT(B14:I14)=0,"",MAX(0,SUM(B14:I14))))</f>
         <v/>
       </c>
-      <c r="N14" s="23" t="str">
+      <c r="N14" s="26" t="str">
         <f aca="false">IF(L14="Sim","NÃO AVALIÁVEL",IF(M14="","",IF(K14="Sim","IV",IF(J14="Sim",IF(M14&lt;=64,"I",IF(M14&lt;=141,"II",IF(M14&lt;=230,"III","IV"))),IF(M14&lt;=58,"I",IF(M14&lt;=127,"II",IF(M14&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O14" s="20"/>
-      <c r="P14" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="32" t="str">
+      <c r="P14" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="34" t="str">
         <f aca="false">IFERROR(MEDIAN(M4:M53),"")</f>
         <v/>
       </c>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="str">
+      <c r="A15" s="26" t="str">
         <f aca="false">IF(Protocolos!A15="","",Protocolos!A15)</f>
         <v/>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="23" t="str">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="26" t="str">
         <f aca="false">IF(L15="Sim","",IF(COUNT(B15:I15)=0,"",MAX(0,SUM(B15:I15))))</f>
         <v/>
       </c>
-      <c r="N15" s="23" t="str">
+      <c r="N15" s="26" t="str">
         <f aca="false">IF(L15="Sim","NÃO AVALIÁVEL",IF(M15="","",IF(K15="Sim","IV",IF(J15="Sim",IF(M15&lt;=64,"I",IF(M15&lt;=141,"II",IF(M15&lt;=230,"III","IV"))),IF(M15&lt;=58,"I",IF(M15&lt;=127,"II",IF(M15&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O15" s="20"/>
-      <c r="P15" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q15" s="32" t="str">
+      <c r="P15" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q15" s="34" t="str">
         <f aca="false">IFERROR(AVERAGE(M4:M53),"")</f>
         <v/>
       </c>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="str">
+      <c r="A16" s="26" t="str">
         <f aca="false">IF(Protocolos!A16="","",Protocolos!A16)</f>
         <v/>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="23" t="str">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="26" t="str">
         <f aca="false">IF(L16="Sim","",IF(COUNT(B16:I16)=0,"",MAX(0,SUM(B16:I16))))</f>
         <v/>
       </c>
-      <c r="N16" s="23" t="str">
+      <c r="N16" s="26" t="str">
         <f aca="false">IF(L16="Sim","NÃO AVALIÁVEL",IF(M16="","",IF(K16="Sim","IV",IF(J16="Sim",IF(M16&lt;=64,"I",IF(M16&lt;=141,"II",IF(M16&lt;=230,"III","IV"))),IF(M16&lt;=58,"I",IF(M16&lt;=127,"II",IF(M16&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O16" s="20"/>
-      <c r="P16" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q16" s="32" t="str">
+      <c r="P16" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q16" s="34" t="str">
         <f aca="false">IFERROR(STDEV(M4:M53),"")</f>
         <v/>
       </c>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="str">
+      <c r="A17" s="26" t="str">
         <f aca="false">IF(Protocolos!A17="","",Protocolos!A17)</f>
         <v/>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="23" t="str">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="26" t="str">
         <f aca="false">IF(L17="Sim","",IF(COUNT(B17:I17)=0,"",MAX(0,SUM(B17:I17))))</f>
         <v/>
       </c>
-      <c r="N17" s="23" t="str">
+      <c r="N17" s="26" t="str">
         <f aca="false">IF(L17="Sim","NÃO AVALIÁVEL",IF(M17="","",IF(K17="Sim","IV",IF(J17="Sim",IF(M17&lt;=64,"I",IF(M17&lt;=141,"II",IF(M17&lt;=230,"III","IV"))),IF(M17&lt;=58,"I",IF(M17&lt;=127,"II",IF(M17&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O17" s="20"/>
-      <c r="P17" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" s="32" t="n">
+      <c r="P17" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="34" t="n">
         <f aca="false">IFERROR(MIN(M4:M53),"")</f>
         <v>0</v>
       </c>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="str">
+      <c r="A18" s="26" t="str">
         <f aca="false">IF(Protocolos!A18="","",Protocolos!A18)</f>
         <v/>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="23" t="str">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="26" t="str">
         <f aca="false">IF(L18="Sim","",IF(COUNT(B18:I18)=0,"",MAX(0,SUM(B18:I18))))</f>
         <v/>
       </c>
-      <c r="N18" s="23" t="str">
+      <c r="N18" s="26" t="str">
         <f aca="false">IF(L18="Sim","NÃO AVALIÁVEL",IF(M18="","",IF(K18="Sim","IV",IF(J18="Sim",IF(M18&lt;=64,"I",IF(M18&lt;=141,"II",IF(M18&lt;=230,"III","IV"))),IF(M18&lt;=58,"I",IF(M18&lt;=127,"II",IF(M18&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O18" s="20"/>
-      <c r="P18" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q18" s="32" t="n">
+      <c r="P18" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="34" t="n">
         <f aca="false">IFERROR(MAX(M4:M53),"")</f>
         <v>0</v>
       </c>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="str">
+      <c r="A19" s="26" t="str">
         <f aca="false">IF(Protocolos!A19="","",Protocolos!A19)</f>
         <v/>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="23" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="26" t="str">
         <f aca="false">IF(L19="Sim","",IF(COUNT(B19:I19)=0,"",MAX(0,SUM(B19:I19))))</f>
         <v/>
       </c>
-      <c r="N19" s="23" t="str">
+      <c r="N19" s="26" t="str">
         <f aca="false">IF(L19="Sim","NÃO AVALIÁVEL",IF(M19="","",IF(K19="Sim","IV",IF(J19="Sim",IF(M19&lt;=64,"I",IF(M19&lt;=141,"II",IF(M19&lt;=230,"III","IV"))),IF(M19&lt;=58,"I",IF(M19&lt;=127,"II",IF(M19&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="str">
+      <c r="A20" s="26" t="str">
         <f aca="false">IF(Protocolos!A20="","",Protocolos!A20)</f>
         <v/>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="23" t="str">
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="26" t="str">
         <f aca="false">IF(L20="Sim","",IF(COUNT(B20:I20)=0,"",MAX(0,SUM(B20:I20))))</f>
         <v/>
       </c>
-      <c r="N20" s="23" t="str">
+      <c r="N20" s="26" t="str">
         <f aca="false">IF(L20="Sim","NÃO AVALIÁVEL",IF(M20="","",IF(K20="Sim","IV",IF(J20="Sim",IF(M20&lt;=64,"I",IF(M20&lt;=141,"II",IF(M20&lt;=230,"III","IV"))),IF(M20&lt;=58,"I",IF(M20&lt;=127,"II",IF(M20&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="str">
+      <c r="A21" s="26" t="str">
         <f aca="false">IF(Protocolos!A21="","",Protocolos!A21)</f>
         <v/>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="23" t="str">
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="26" t="str">
         <f aca="false">IF(L21="Sim","",IF(COUNT(B21:I21)=0,"",MAX(0,SUM(B21:I21))))</f>
         <v/>
       </c>
-      <c r="N21" s="23" t="str">
+      <c r="N21" s="26" t="str">
         <f aca="false">IF(L21="Sim","NÃO AVALIÁVEL",IF(M21="","",IF(K21="Sim","IV",IF(J21="Sim",IF(M21&lt;=64,"I",IF(M21&lt;=141,"II",IF(M21&lt;=230,"III","IV"))),IF(M21&lt;=58,"I",IF(M21&lt;=127,"II",IF(M21&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="str">
+      <c r="A22" s="26" t="str">
         <f aca="false">IF(Protocolos!A22="","",Protocolos!A22)</f>
         <v/>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="23" t="str">
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="26" t="str">
         <f aca="false">IF(L22="Sim","",IF(COUNT(B22:I22)=0,"",MAX(0,SUM(B22:I22))))</f>
         <v/>
       </c>
-      <c r="N22" s="23" t="str">
+      <c r="N22" s="26" t="str">
         <f aca="false">IF(L22="Sim","NÃO AVALIÁVEL",IF(M22="","",IF(K22="Sim","IV",IF(J22="Sim",IF(M22&lt;=64,"I",IF(M22&lt;=141,"II",IF(M22&lt;=230,"III","IV"))),IF(M22&lt;=58,"I",IF(M22&lt;=127,"II",IF(M22&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="str">
+      <c r="A23" s="26" t="str">
         <f aca="false">IF(Protocolos!A23="","",Protocolos!A23)</f>
         <v/>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="23" t="str">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="26" t="str">
         <f aca="false">IF(L23="Sim","",IF(COUNT(B23:I23)=0,"",MAX(0,SUM(B23:I23))))</f>
         <v/>
       </c>
-      <c r="N23" s="23" t="str">
+      <c r="N23" s="26" t="str">
         <f aca="false">IF(L23="Sim","NÃO AVALIÁVEL",IF(M23="","",IF(K23="Sim","IV",IF(J23="Sim",IF(M23&lt;=64,"I",IF(M23&lt;=141,"II",IF(M23&lt;=230,"III","IV"))),IF(M23&lt;=58,"I",IF(M23&lt;=127,"II",IF(M23&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="str">
+      <c r="A24" s="26" t="str">
         <f aca="false">IF(Protocolos!A24="","",Protocolos!A24)</f>
         <v/>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="23" t="str">
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="26" t="str">
         <f aca="false">IF(L24="Sim","",IF(COUNT(B24:I24)=0,"",MAX(0,SUM(B24:I24))))</f>
         <v/>
       </c>
-      <c r="N24" s="23" t="str">
+      <c r="N24" s="26" t="str">
         <f aca="false">IF(L24="Sim","NÃO AVALIÁVEL",IF(M24="","",IF(K24="Sim","IV",IF(J24="Sim",IF(M24&lt;=64,"I",IF(M24&lt;=141,"II",IF(M24&lt;=230,"III","IV"))),IF(M24&lt;=58,"I",IF(M24&lt;=127,"II",IF(M24&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="str">
+      <c r="A25" s="26" t="str">
         <f aca="false">IF(Protocolos!A25="","",Protocolos!A25)</f>
         <v/>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="23" t="str">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="26" t="str">
         <f aca="false">IF(L25="Sim","",IF(COUNT(B25:I25)=0,"",MAX(0,SUM(B25:I25))))</f>
         <v/>
       </c>
-      <c r="N25" s="23" t="str">
+      <c r="N25" s="26" t="str">
         <f aca="false">IF(L25="Sim","NÃO AVALIÁVEL",IF(M25="","",IF(K25="Sim","IV",IF(J25="Sim",IF(M25&lt;=64,"I",IF(M25&lt;=141,"II",IF(M25&lt;=230,"III","IV"))),IF(M25&lt;=58,"I",IF(M25&lt;=127,"II",IF(M25&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="str">
+      <c r="A26" s="26" t="str">
         <f aca="false">IF(Protocolos!A26="","",Protocolos!A26)</f>
         <v/>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="23" t="str">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="26" t="str">
         <f aca="false">IF(L26="Sim","",IF(COUNT(B26:I26)=0,"",MAX(0,SUM(B26:I26))))</f>
         <v/>
       </c>
-      <c r="N26" s="23" t="str">
+      <c r="N26" s="26" t="str">
         <f aca="false">IF(L26="Sim","NÃO AVALIÁVEL",IF(M26="","",IF(K26="Sim","IV",IF(J26="Sim",IF(M26&lt;=64,"I",IF(M26&lt;=141,"II",IF(M26&lt;=230,"III","IV"))),IF(M26&lt;=58,"I",IF(M26&lt;=127,"II",IF(M26&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="str">
+      <c r="A27" s="26" t="str">
         <f aca="false">IF(Protocolos!A27="","",Protocolos!A27)</f>
         <v/>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="23" t="str">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="26" t="str">
         <f aca="false">IF(L27="Sim","",IF(COUNT(B27:I27)=0,"",MAX(0,SUM(B27:I27))))</f>
         <v/>
       </c>
-      <c r="N27" s="23" t="str">
+      <c r="N27" s="26" t="str">
         <f aca="false">IF(L27="Sim","NÃO AVALIÁVEL",IF(M27="","",IF(K27="Sim","IV",IF(J27="Sim",IF(M27&lt;=64,"I",IF(M27&lt;=141,"II",IF(M27&lt;=230,"III","IV"))),IF(M27&lt;=58,"I",IF(M27&lt;=127,"II",IF(M27&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="str">
+      <c r="A28" s="26" t="str">
         <f aca="false">IF(Protocolos!A28="","",Protocolos!A28)</f>
         <v/>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="23" t="str">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="26" t="str">
         <f aca="false">IF(L28="Sim","",IF(COUNT(B28:I28)=0,"",MAX(0,SUM(B28:I28))))</f>
         <v/>
       </c>
-      <c r="N28" s="23" t="str">
+      <c r="N28" s="26" t="str">
         <f aca="false">IF(L28="Sim","NÃO AVALIÁVEL",IF(M28="","",IF(K28="Sim","IV",IF(J28="Sim",IF(M28&lt;=64,"I",IF(M28&lt;=141,"II",IF(M28&lt;=230,"III","IV"))),IF(M28&lt;=58,"I",IF(M28&lt;=127,"II",IF(M28&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="str">
+      <c r="A29" s="26" t="str">
         <f aca="false">IF(Protocolos!A29="","",Protocolos!A29)</f>
         <v/>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="23" t="str">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="26" t="str">
         <f aca="false">IF(L29="Sim","",IF(COUNT(B29:I29)=0,"",MAX(0,SUM(B29:I29))))</f>
         <v/>
       </c>
-      <c r="N29" s="23" t="str">
+      <c r="N29" s="26" t="str">
         <f aca="false">IF(L29="Sim","NÃO AVALIÁVEL",IF(M29="","",IF(K29="Sim","IV",IF(J29="Sim",IF(M29&lt;=64,"I",IF(M29&lt;=141,"II",IF(M29&lt;=230,"III","IV"))),IF(M29&lt;=58,"I",IF(M29&lt;=127,"II",IF(M29&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="str">
+      <c r="A30" s="26" t="str">
         <f aca="false">IF(Protocolos!A30="","",Protocolos!A30)</f>
         <v/>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="23" t="str">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="26" t="str">
         <f aca="false">IF(L30="Sim","",IF(COUNT(B30:I30)=0,"",MAX(0,SUM(B30:I30))))</f>
         <v/>
       </c>
-      <c r="N30" s="23" t="str">
+      <c r="N30" s="26" t="str">
         <f aca="false">IF(L30="Sim","NÃO AVALIÁVEL",IF(M30="","",IF(K30="Sim","IV",IF(J30="Sim",IF(M30&lt;=64,"I",IF(M30&lt;=141,"II",IF(M30&lt;=230,"III","IV"))),IF(M30&lt;=58,"I",IF(M30&lt;=127,"II",IF(M30&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="str">
+      <c r="A31" s="26" t="str">
         <f aca="false">IF(Protocolos!A31="","",Protocolos!A31)</f>
         <v/>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="23" t="str">
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="26" t="str">
         <f aca="false">IF(L31="Sim","",IF(COUNT(B31:I31)=0,"",MAX(0,SUM(B31:I31))))</f>
         <v/>
       </c>
-      <c r="N31" s="23" t="str">
+      <c r="N31" s="26" t="str">
         <f aca="false">IF(L31="Sim","NÃO AVALIÁVEL",IF(M31="","",IF(K31="Sim","IV",IF(J31="Sim",IF(M31&lt;=64,"I",IF(M31&lt;=141,"II",IF(M31&lt;=230,"III","IV"))),IF(M31&lt;=58,"I",IF(M31&lt;=127,"II",IF(M31&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="str">
+      <c r="A32" s="26" t="str">
         <f aca="false">IF(Protocolos!A32="","",Protocolos!A32)</f>
         <v/>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="23" t="str">
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="26" t="str">
         <f aca="false">IF(L32="Sim","",IF(COUNT(B32:I32)=0,"",MAX(0,SUM(B32:I32))))</f>
         <v/>
       </c>
-      <c r="N32" s="23" t="str">
+      <c r="N32" s="26" t="str">
         <f aca="false">IF(L32="Sim","NÃO AVALIÁVEL",IF(M32="","",IF(K32="Sim","IV",IF(J32="Sim",IF(M32&lt;=64,"I",IF(M32&lt;=141,"II",IF(M32&lt;=230,"III","IV"))),IF(M32&lt;=58,"I",IF(M32&lt;=127,"II",IF(M32&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="str">
+      <c r="A33" s="26" t="str">
         <f aca="false">IF(Protocolos!A33="","",Protocolos!A33)</f>
         <v/>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="23" t="str">
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="26" t="str">
         <f aca="false">IF(L33="Sim","",IF(COUNT(B33:I33)=0,"",MAX(0,SUM(B33:I33))))</f>
         <v/>
       </c>
-      <c r="N33" s="23" t="str">
+      <c r="N33" s="26" t="str">
         <f aca="false">IF(L33="Sim","NÃO AVALIÁVEL",IF(M33="","",IF(K33="Sim","IV",IF(J33="Sim",IF(M33&lt;=64,"I",IF(M33&lt;=141,"II",IF(M33&lt;=230,"III","IV"))),IF(M33&lt;=58,"I",IF(M33&lt;=127,"II",IF(M33&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="str">
+      <c r="A34" s="26" t="str">
         <f aca="false">IF(Protocolos!A34="","",Protocolos!A34)</f>
         <v/>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="23" t="str">
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="26" t="str">
         <f aca="false">IF(L34="Sim","",IF(COUNT(B34:I34)=0,"",MAX(0,SUM(B34:I34))))</f>
         <v/>
       </c>
-      <c r="N34" s="23" t="str">
+      <c r="N34" s="26" t="str">
         <f aca="false">IF(L34="Sim","NÃO AVALIÁVEL",IF(M34="","",IF(K34="Sim","IV",IF(J34="Sim",IF(M34&lt;=64,"I",IF(M34&lt;=141,"II",IF(M34&lt;=230,"III","IV"))),IF(M34&lt;=58,"I",IF(M34&lt;=127,"II",IF(M34&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="str">
+      <c r="A35" s="26" t="str">
         <f aca="false">IF(Protocolos!A35="","",Protocolos!A35)</f>
         <v/>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="23" t="str">
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="26" t="str">
         <f aca="false">IF(L35="Sim","",IF(COUNT(B35:I35)=0,"",MAX(0,SUM(B35:I35))))</f>
         <v/>
       </c>
-      <c r="N35" s="23" t="str">
+      <c r="N35" s="26" t="str">
         <f aca="false">IF(L35="Sim","NÃO AVALIÁVEL",IF(M35="","",IF(K35="Sim","IV",IF(J35="Sim",IF(M35&lt;=64,"I",IF(M35&lt;=141,"II",IF(M35&lt;=230,"III","IV"))),IF(M35&lt;=58,"I",IF(M35&lt;=127,"II",IF(M35&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="str">
+      <c r="A36" s="26" t="str">
         <f aca="false">IF(Protocolos!A36="","",Protocolos!A36)</f>
         <v/>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="23" t="str">
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="26" t="str">
         <f aca="false">IF(L36="Sim","",IF(COUNT(B36:I36)=0,"",MAX(0,SUM(B36:I36))))</f>
         <v/>
       </c>
-      <c r="N36" s="23" t="str">
+      <c r="N36" s="26" t="str">
         <f aca="false">IF(L36="Sim","NÃO AVALIÁVEL",IF(M36="","",IF(K36="Sim","IV",IF(J36="Sim",IF(M36&lt;=64,"I",IF(M36&lt;=141,"II",IF(M36&lt;=230,"III","IV"))),IF(M36&lt;=58,"I",IF(M36&lt;=127,"II",IF(M36&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O36" s="20"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="str">
+      <c r="A37" s="26" t="str">
         <f aca="false">IF(Protocolos!A37="","",Protocolos!A37)</f>
         <v/>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="23" t="str">
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="26" t="str">
         <f aca="false">IF(L37="Sim","",IF(COUNT(B37:I37)=0,"",MAX(0,SUM(B37:I37))))</f>
         <v/>
       </c>
-      <c r="N37" s="23" t="str">
+      <c r="N37" s="26" t="str">
         <f aca="false">IF(L37="Sim","NÃO AVALIÁVEL",IF(M37="","",IF(K37="Sim","IV",IF(J37="Sim",IF(M37&lt;=64,"I",IF(M37&lt;=141,"II",IF(M37&lt;=230,"III","IV"))),IF(M37&lt;=58,"I",IF(M37&lt;=127,"II",IF(M37&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="str">
+      <c r="A38" s="26" t="str">
         <f aca="false">IF(Protocolos!A38="","",Protocolos!A38)</f>
         <v/>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="23" t="str">
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="26" t="str">
         <f aca="false">IF(L38="Sim","",IF(COUNT(B38:I38)=0,"",MAX(0,SUM(B38:I38))))</f>
         <v/>
       </c>
-      <c r="N38" s="23" t="str">
+      <c r="N38" s="26" t="str">
         <f aca="false">IF(L38="Sim","NÃO AVALIÁVEL",IF(M38="","",IF(K38="Sim","IV",IF(J38="Sim",IF(M38&lt;=64,"I",IF(M38&lt;=141,"II",IF(M38&lt;=230,"III","IV"))),IF(M38&lt;=58,"I",IF(M38&lt;=127,"II",IF(M38&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23" t="str">
+      <c r="A39" s="26" t="str">
         <f aca="false">IF(Protocolos!A39="","",Protocolos!A39)</f>
         <v/>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="23" t="str">
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="26" t="str">
         <f aca="false">IF(L39="Sim","",IF(COUNT(B39:I39)=0,"",MAX(0,SUM(B39:I39))))</f>
         <v/>
       </c>
-      <c r="N39" s="23" t="str">
+      <c r="N39" s="26" t="str">
         <f aca="false">IF(L39="Sim","NÃO AVALIÁVEL",IF(M39="","",IF(K39="Sim","IV",IF(J39="Sim",IF(M39&lt;=64,"I",IF(M39&lt;=141,"II",IF(M39&lt;=230,"III","IV"))),IF(M39&lt;=58,"I",IF(M39&lt;=127,"II",IF(M39&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="str">
+      <c r="A40" s="26" t="str">
         <f aca="false">IF(Protocolos!A40="","",Protocolos!A40)</f>
         <v/>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="23" t="str">
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="26" t="str">
         <f aca="false">IF(L40="Sim","",IF(COUNT(B40:I40)=0,"",MAX(0,SUM(B40:I40))))</f>
         <v/>
       </c>
-      <c r="N40" s="23" t="str">
+      <c r="N40" s="26" t="str">
         <f aca="false">IF(L40="Sim","NÃO AVALIÁVEL",IF(M40="","",IF(K40="Sim","IV",IF(J40="Sim",IF(M40&lt;=64,"I",IF(M40&lt;=141,"II",IF(M40&lt;=230,"III","IV"))),IF(M40&lt;=58,"I",IF(M40&lt;=127,"II",IF(M40&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="str">
+      <c r="A41" s="26" t="str">
         <f aca="false">IF(Protocolos!A41="","",Protocolos!A41)</f>
         <v/>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="23" t="str">
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="26" t="str">
         <f aca="false">IF(L41="Sim","",IF(COUNT(B41:I41)=0,"",MAX(0,SUM(B41:I41))))</f>
         <v/>
       </c>
-      <c r="N41" s="23" t="str">
+      <c r="N41" s="26" t="str">
         <f aca="false">IF(L41="Sim","NÃO AVALIÁVEL",IF(M41="","",IF(K41="Sim","IV",IF(J41="Sim",IF(M41&lt;=64,"I",IF(M41&lt;=141,"II",IF(M41&lt;=230,"III","IV"))),IF(M41&lt;=58,"I",IF(M41&lt;=127,"II",IF(M41&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23" t="str">
+      <c r="A42" s="26" t="str">
         <f aca="false">IF(Protocolos!A42="","",Protocolos!A42)</f>
         <v/>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
-      <c r="L42" s="24"/>
-      <c r="M42" s="23" t="str">
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="26" t="str">
         <f aca="false">IF(L42="Sim","",IF(COUNT(B42:I42)=0,"",MAX(0,SUM(B42:I42))))</f>
         <v/>
       </c>
-      <c r="N42" s="23" t="str">
+      <c r="N42" s="26" t="str">
         <f aca="false">IF(L42="Sim","NÃO AVALIÁVEL",IF(M42="","",IF(K42="Sim","IV",IF(J42="Sim",IF(M42&lt;=64,"I",IF(M42&lt;=141,"II",IF(M42&lt;=230,"III","IV"))),IF(M42&lt;=58,"I",IF(M42&lt;=127,"II",IF(M42&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="str">
+      <c r="A43" s="26" t="str">
         <f aca="false">IF(Protocolos!A43="","",Protocolos!A43)</f>
         <v/>
       </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="23" t="str">
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="26" t="str">
         <f aca="false">IF(L43="Sim","",IF(COUNT(B43:I43)=0,"",MAX(0,SUM(B43:I43))))</f>
         <v/>
       </c>
-      <c r="N43" s="23" t="str">
+      <c r="N43" s="26" t="str">
         <f aca="false">IF(L43="Sim","NÃO AVALIÁVEL",IF(M43="","",IF(K43="Sim","IV",IF(J43="Sim",IF(M43&lt;=64,"I",IF(M43&lt;=141,"II",IF(M43&lt;=230,"III","IV"))),IF(M43&lt;=58,"I",IF(M43&lt;=127,"II",IF(M43&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23" t="str">
+      <c r="A44" s="26" t="str">
         <f aca="false">IF(Protocolos!A44="","",Protocolos!A44)</f>
         <v/>
       </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="23" t="str">
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="26" t="str">
         <f aca="false">IF(L44="Sim","",IF(COUNT(B44:I44)=0,"",MAX(0,SUM(B44:I44))))</f>
         <v/>
       </c>
-      <c r="N44" s="23" t="str">
+      <c r="N44" s="26" t="str">
         <f aca="false">IF(L44="Sim","NÃO AVALIÁVEL",IF(M44="","",IF(K44="Sim","IV",IF(J44="Sim",IF(M44&lt;=64,"I",IF(M44&lt;=141,"II",IF(M44&lt;=230,"III","IV"))),IF(M44&lt;=58,"I",IF(M44&lt;=127,"II",IF(M44&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23" t="str">
+      <c r="A45" s="26" t="str">
         <f aca="false">IF(Protocolos!A45="","",Protocolos!A45)</f>
         <v/>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="23" t="str">
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27"/>
+      <c r="K45" s="27"/>
+      <c r="L45" s="27"/>
+      <c r="M45" s="26" t="str">
         <f aca="false">IF(L45="Sim","",IF(COUNT(B45:I45)=0,"",MAX(0,SUM(B45:I45))))</f>
         <v/>
       </c>
-      <c r="N45" s="23" t="str">
+      <c r="N45" s="26" t="str">
         <f aca="false">IF(L45="Sim","NÃO AVALIÁVEL",IF(M45="","",IF(K45="Sim","IV",IF(J45="Sim",IF(M45&lt;=64,"I",IF(M45&lt;=141,"II",IF(M45&lt;=230,"III","IV"))),IF(M45&lt;=58,"I",IF(M45&lt;=127,"II",IF(M45&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23" t="str">
+      <c r="A46" s="26" t="str">
         <f aca="false">IF(Protocolos!A46="","",Protocolos!A46)</f>
         <v/>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="23" t="str">
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="26" t="str">
         <f aca="false">IF(L46="Sim","",IF(COUNT(B46:I46)=0,"",MAX(0,SUM(B46:I46))))</f>
         <v/>
       </c>
-      <c r="N46" s="23" t="str">
+      <c r="N46" s="26" t="str">
         <f aca="false">IF(L46="Sim","NÃO AVALIÁVEL",IF(M46="","",IF(K46="Sim","IV",IF(J46="Sim",IF(M46&lt;=64,"I",IF(M46&lt;=141,"II",IF(M46&lt;=230,"III","IV"))),IF(M46&lt;=58,"I",IF(M46&lt;=127,"II",IF(M46&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O46" s="20"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="str">
+      <c r="A47" s="26" t="str">
         <f aca="false">IF(Protocolos!A47="","",Protocolos!A47)</f>
         <v/>
       </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="23" t="str">
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
+      <c r="K47" s="27"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="26" t="str">
         <f aca="false">IF(L47="Sim","",IF(COUNT(B47:I47)=0,"",MAX(0,SUM(B47:I47))))</f>
         <v/>
       </c>
-      <c r="N47" s="23" t="str">
+      <c r="N47" s="26" t="str">
         <f aca="false">IF(L47="Sim","NÃO AVALIÁVEL",IF(M47="","",IF(K47="Sim","IV",IF(J47="Sim",IF(M47&lt;=64,"I",IF(M47&lt;=141,"II",IF(M47&lt;=230,"III","IV"))),IF(M47&lt;=58,"I",IF(M47&lt;=127,"II",IF(M47&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O47" s="20"/>
-      <c r="P47" s="20"/>
-      <c r="Q47" s="20"/>
-      <c r="R47" s="20"/>
-      <c r="S47" s="20"/>
-      <c r="T47" s="20"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="str">
+      <c r="A48" s="26" t="str">
         <f aca="false">IF(Protocolos!A48="","",Protocolos!A48)</f>
         <v/>
       </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="23" t="str">
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="26" t="str">
         <f aca="false">IF(L48="Sim","",IF(COUNT(B48:I48)=0,"",MAX(0,SUM(B48:I48))))</f>
         <v/>
       </c>
-      <c r="N48" s="23" t="str">
+      <c r="N48" s="26" t="str">
         <f aca="false">IF(L48="Sim","NÃO AVALIÁVEL",IF(M48="","",IF(K48="Sim","IV",IF(J48="Sim",IF(M48&lt;=64,"I",IF(M48&lt;=141,"II",IF(M48&lt;=230,"III","IV"))),IF(M48&lt;=58,"I",IF(M48&lt;=127,"II",IF(M48&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O48" s="20"/>
-      <c r="P48" s="20"/>
-      <c r="Q48" s="20"/>
-      <c r="R48" s="20"/>
-      <c r="S48" s="20"/>
-      <c r="T48" s="20"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="str">
+      <c r="A49" s="26" t="str">
         <f aca="false">IF(Protocolos!A49="","",Protocolos!A49)</f>
         <v/>
       </c>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="23" t="str">
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="26" t="str">
         <f aca="false">IF(L49="Sim","",IF(COUNT(B49:I49)=0,"",MAX(0,SUM(B49:I49))))</f>
         <v/>
       </c>
-      <c r="N49" s="23" t="str">
+      <c r="N49" s="26" t="str">
         <f aca="false">IF(L49="Sim","NÃO AVALIÁVEL",IF(M49="","",IF(K49="Sim","IV",IF(J49="Sim",IF(M49&lt;=64,"I",IF(M49&lt;=141,"II",IF(M49&lt;=230,"III","IV"))),IF(M49&lt;=58,"I",IF(M49&lt;=127,"II",IF(M49&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O49" s="20"/>
-      <c r="P49" s="20"/>
-      <c r="Q49" s="20"/>
-      <c r="R49" s="20"/>
-      <c r="S49" s="20"/>
-      <c r="T49" s="20"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="str">
+      <c r="A50" s="26" t="str">
         <f aca="false">IF(Protocolos!A50="","",Protocolos!A50)</f>
         <v/>
       </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="23" t="str">
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27"/>
+      <c r="K50" s="27"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="26" t="str">
         <f aca="false">IF(L50="Sim","",IF(COUNT(B50:I50)=0,"",MAX(0,SUM(B50:I50))))</f>
         <v/>
       </c>
-      <c r="N50" s="23" t="str">
+      <c r="N50" s="26" t="str">
         <f aca="false">IF(L50="Sim","NÃO AVALIÁVEL",IF(M50="","",IF(K50="Sim","IV",IF(J50="Sim",IF(M50&lt;=64,"I",IF(M50&lt;=141,"II",IF(M50&lt;=230,"III","IV"))),IF(M50&lt;=58,"I",IF(M50&lt;=127,"II",IF(M50&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O50" s="20"/>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="20"/>
-      <c r="R50" s="20"/>
-      <c r="S50" s="20"/>
-      <c r="T50" s="20"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="str">
+      <c r="A51" s="26" t="str">
         <f aca="false">IF(Protocolos!A51="","",Protocolos!A51)</f>
         <v/>
       </c>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="23" t="str">
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="27"/>
+      <c r="K51" s="27"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="26" t="str">
         <f aca="false">IF(L51="Sim","",IF(COUNT(B51:I51)=0,"",MAX(0,SUM(B51:I51))))</f>
         <v/>
       </c>
-      <c r="N51" s="23" t="str">
+      <c r="N51" s="26" t="str">
         <f aca="false">IF(L51="Sim","NÃO AVALIÁVEL",IF(M51="","",IF(K51="Sim","IV",IF(J51="Sim",IF(M51&lt;=64,"I",IF(M51&lt;=141,"II",IF(M51&lt;=230,"III","IV"))),IF(M51&lt;=58,"I",IF(M51&lt;=127,"II",IF(M51&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O51" s="20"/>
-      <c r="P51" s="20"/>
-      <c r="Q51" s="20"/>
-      <c r="R51" s="20"/>
-      <c r="S51" s="20"/>
-      <c r="T51" s="20"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="str">
+      <c r="A52" s="26" t="str">
         <f aca="false">IF(Protocolos!A52="","",Protocolos!A52)</f>
         <v/>
       </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="23" t="str">
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="27"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="26" t="str">
         <f aca="false">IF(L52="Sim","",IF(COUNT(B52:I52)=0,"",MAX(0,SUM(B52:I52))))</f>
         <v/>
       </c>
-      <c r="N52" s="23" t="str">
+      <c r="N52" s="26" t="str">
         <f aca="false">IF(L52="Sim","NÃO AVALIÁVEL",IF(M52="","",IF(K52="Sim","IV",IF(J52="Sim",IF(M52&lt;=64,"I",IF(M52&lt;=141,"II",IF(M52&lt;=230,"III","IV"))),IF(M52&lt;=58,"I",IF(M52&lt;=127,"II",IF(M52&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O52" s="20"/>
-      <c r="P52" s="20"/>
-      <c r="Q52" s="20"/>
-      <c r="R52" s="20"/>
-      <c r="S52" s="20"/>
-      <c r="T52" s="20"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23" t="str">
+      <c r="A53" s="26" t="str">
         <f aca="false">IF(Protocolos!A53="","",Protocolos!A53)</f>
         <v/>
       </c>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="23" t="str">
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="26" t="str">
         <f aca="false">IF(L53="Sim","",IF(COUNT(B53:I53)=0,"",MAX(0,SUM(B53:I53))))</f>
         <v/>
       </c>
-      <c r="N53" s="23" t="str">
+      <c r="N53" s="26" t="str">
         <f aca="false">IF(L53="Sim","NÃO AVALIÁVEL",IF(M53="","",IF(K53="Sim","IV",IF(J53="Sim",IF(M53&lt;=64,"I",IF(M53&lt;=141,"II",IF(M53&lt;=230,"III","IV"))),IF(M53&lt;=58,"I",IF(M53&lt;=127,"II",IF(M53&lt;=208,"III","IV")))))))</f>
         <v/>
       </c>
-      <c r="O53" s="20"/>
-      <c r="P53" s="20"/>
-      <c r="Q53" s="20"/>
-      <c r="R53" s="20"/>
-      <c r="S53" s="20"/>
-      <c r="T53" s="20"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="20"/>
-      <c r="R54" s="20"/>
-      <c r="S54" s="20"/>
-      <c r="T54" s="20"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="20"/>
-      <c r="O55" s="20"/>
-      <c r="P55" s="20"/>
-      <c r="Q55" s="20"/>
-      <c r="R55" s="20"/>
-      <c r="S55" s="20"/>
-      <c r="T55" s="20"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-      <c r="Q56" s="20"/>
-      <c r="R56" s="20"/>
-      <c r="S56" s="20"/>
-      <c r="T56" s="20"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="20"/>
-      <c r="Q57" s="20"/>
-      <c r="R57" s="20"/>
-      <c r="S57" s="20"/>
-      <c r="T57" s="20"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
-      <c r="Q58" s="20"/>
-      <c r="R58" s="20"/>
-      <c r="S58" s="20"/>
-      <c r="T58" s="20"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20"/>
-      <c r="S59" s="20"/>
-      <c r="T59" s="20"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
-      <c r="Q60" s="20"/>
-      <c r="R60" s="20"/>
-      <c r="S60" s="20"/>
-      <c r="T60" s="20"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4438,7 +4209,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4446,7 +4217,7 @@
     </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -4454,19 +4225,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
@@ -4491,16 +4262,16 @@
         <v/>
       </c>
       <c r="G4" s="8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4521,7 +4292,7 @@
         <v/>
       </c>
       <c r="F5" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">COUNTIFS(B4:B53,"I",C4:C53,"I")</f>
@@ -4558,7 +4329,7 @@
         <v/>
       </c>
       <c r="F6" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G6" s="16" t="n">
         <f aca="false">COUNTIFS(B4:B53,"II",C4:C53,"I")</f>
@@ -4595,7 +4366,7 @@
         <v/>
       </c>
       <c r="F7" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">COUNTIFS(B4:B53,"III",C4:C53,"I")</f>
@@ -4632,7 +4403,7 @@
         <v/>
       </c>
       <c r="F8" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G8" s="16" t="n">
         <f aca="false">COUNTIFS(B4:B53,"IV",C4:C53,"I")</f>
@@ -4687,10 +4458,10 @@
         <v/>
       </c>
       <c r="F10" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4710,8 +4481,8 @@
         <f aca="false">IF(OR(B11="",C11="",ISNA(MATCH(B11,{"I","II","III","IV"},0)),ISNA(MATCH(C11,{"I","II","III","IV"},0))),"",IF(B11=C11,"Sim","Não"))</f>
         <v/>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>85</v>
+      <c r="F11" s="35" t="s">
+        <v>90</v>
       </c>
       <c r="G11" s="16" t="n">
         <f aca="false">COUNTIF(D4:D53,"Sim")+COUNTIF(D4:D53,"Não")</f>
@@ -4735,8 +4506,8 @@
         <f aca="false">IF(OR(B12="",C12="",ISNA(MATCH(B12,{"I","II","III","IV"},0)),ISNA(MATCH(C12,{"I","II","III","IV"},0))),"",IF(B12=C12,"Sim","Não"))</f>
         <v/>
       </c>
-      <c r="F12" s="33" t="s">
-        <v>86</v>
+      <c r="F12" s="35" t="s">
+        <v>91</v>
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">COUNTIF(D4:D53,"Sim")</f>
@@ -4760,10 +4531,10 @@
         <f aca="false">IF(OR(B13="",C13="",ISNA(MATCH(B13,{"I","II","III","IV"},0)),ISNA(MATCH(C13,{"I","II","III","IV"},0))),"",IF(B13=C13,"Sim","Não"))</f>
         <v/>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="34" t="str">
+      <c r="F13" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="36" t="str">
         <f aca="false">IF(G11=0,"",G12/G11)</f>
         <v/>
       </c>
@@ -5519,147 +5290,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
-        <v>30</v>
+      <c r="A5" s="38" t="s">
+        <v>31</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">'Versão A'!H4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
-        <v>91</v>
+      <c r="A6" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="B6" s="17" t="str">
         <f aca="false">'Versão A'!H7</f>
         <v/>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>35</v>
+      <c r="A7" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="B7" s="18" t="str">
         <f aca="false">'Versão A'!H9</f>
         <v/>
       </c>
-      <c r="C7" s="37" t="s">
-        <v>92</v>
+      <c r="C7" s="39" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>36</v>
+      <c r="A8" s="38" t="s">
+        <v>37</v>
       </c>
       <c r="B8" s="13" t="str">
         <f aca="false">'Versão A'!H10</f>
         <v/>
       </c>
-      <c r="C8" s="37"/>
+      <c r="C8" s="39"/>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="40" t="str">
+        <f aca="false">'Versão A'!H17</f>
+        <v/>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
+      <c r="A10" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>94</v>
+      <c r="A11" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">'Versão B'!Q9</f>
         <v>0</v>
       </c>
-      <c r="C11" s="37"/>
+      <c r="C11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>95</v>
+      <c r="A12" s="38" t="s">
+        <v>101</v>
       </c>
       <c r="B12" s="17" t="str">
         <f aca="false">'Versão B'!R5</f>
         <v/>
       </c>
-      <c r="C12" s="37"/>
+      <c r="C12" s="39"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>96</v>
+      <c r="A13" s="38" t="s">
+        <v>102</v>
       </c>
       <c r="B13" s="17" t="str">
         <f aca="false">'Versão B'!R6</f>
         <v/>
       </c>
-      <c r="C13" s="37"/>
+      <c r="C13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>97</v>
+      <c r="A14" s="38" t="s">
+        <v>103</v>
       </c>
       <c r="B14" s="17" t="str">
         <f aca="false">'Versão B'!R7</f>
         <v/>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>98</v>
+      <c r="A15" s="38" t="s">
+        <v>104</v>
       </c>
       <c r="B15" s="17" t="str">
         <f aca="false">'Versão B'!R8</f>
         <v/>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="38" t="str">
+      <c r="A16" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="41" t="str">
         <f aca="false">'Versão B'!Q14</f>
         <v/>
       </c>
-      <c r="C16" s="37"/>
+      <c r="C16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>100</v>
+      <c r="A17" s="38" t="s">
+        <v>106</v>
       </c>
       <c r="B17" s="16" t="str">
         <f aca="false">IF('Versão B'!Q17="","",'Versão B'!Q17&amp;" – "&amp;'Versão B'!Q18)</f>
         <v>0 – 0</v>
       </c>
-      <c r="C17" s="37"/>
-    </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>101</v>
+      <c r="C17" s="39"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="B18" s="16" t="str">
         <f aca="false">'Versão B'!Q10&amp;" · "&amp;'Versão B'!Q11</f>
@@ -5667,92 +5447,92 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
+      <c r="A19" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>103</v>
+      <c r="A20" s="38" t="s">
+        <v>109</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">'Triagem A↔B'!G11</f>
         <v>0</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>104</v>
+      <c r="A21" s="38" t="s">
+        <v>110</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">'Triagem A↔B'!G12</f>
         <v>0</v>
       </c>
-      <c r="C21" s="37"/>
+      <c r="C21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="34" t="str">
+      <c r="A22" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="36" t="str">
         <f aca="false">'Triagem A↔B'!G13</f>
         <v/>
       </c>
-      <c r="C22" s="37" t="s">
-        <v>106</v>
+      <c r="C22" s="39" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
+      <c r="A24" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
+      <c r="A25" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
+      <c r="A26" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
+      <c r="A27" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
+      <c r="A28" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
+      <c r="A29" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
+      <c r="A30" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="12">
